--- a/listings.xlsx
+++ b/listings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="172">
   <si>
     <t>Source</t>
   </si>
@@ -35,32 +35,508 @@
     <t>URL</t>
   </si>
   <si>
+    <t>Barnes</t>
+  </si>
+  <si>
+    <t>PARIS 7ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87108484.html</t>
+  </si>
+  <si>
+    <t>PARIS 16ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87141456.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87146307.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87135906.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87108483.html</t>
+  </si>
+  <si>
+    <t>PARIS 5ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-5eme/ref-APM-87168574.html</t>
+  </si>
+  <si>
+    <t>PARIS 13ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-13eme/ref-APM-87108455.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87116409.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87113733.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87133345.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87133281.html</t>
+  </si>
+  <si>
+    <t>PARIS 14ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-14eme/ref-APM-87154855.html</t>
+  </si>
+  <si>
+    <t>PARIS 3ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-3eme/ref-APM-87115895.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-3eme/ref-APM-87145745.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87088202.html</t>
+  </si>
+  <si>
+    <t>PARIS 1ER</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-1er/ref-APM-87107227.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87090950.html</t>
+  </si>
+  <si>
+    <t>PARIS 2ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-2eme/ref-APM-87108371.html</t>
+  </si>
+  <si>
+    <t>PARIS 8ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-87106627.html</t>
+  </si>
+  <si>
+    <t>PARIS 19ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-19eme/ref-APM-87155145.html</t>
+  </si>
+  <si>
+    <t>PARIS 10ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-10eme/ref-APM-87146095.html</t>
+  </si>
+  <si>
+    <t>PARIS 15ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-15eme/ref-APM-87114087.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-15eme/ref-APM-87141762.html</t>
+  </si>
+  <si>
+    <t>PARIS 17ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-17eme/ref-APM-87103528.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-17eme/ref-APM-87115611.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87075933.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-1er/ref-APM-2765878.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-84518447.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86909353.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-85703041.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-87057029.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86922282.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86344622.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-86990123.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87020971.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86965288.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86218331.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-6656135.html</t>
+  </si>
+  <si>
+    <t>PARIS 6ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-86802179.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-4176421.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86731286.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-82258022.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-2766255.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-7410242.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86896328.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86437022.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-84655180.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86823325.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-82367964.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-3eme/ref-APM-7324456.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-2766079.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-17eme/ref-APM-7468343.html</t>
+  </si>
+  <si>
+    <t>PARIS 4ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-4eme/ref-APM-83642472.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-82921741.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-85376050.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-86831290.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-82478963.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86667738.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86739321.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87008418.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86071681.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-85458297.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-82560216.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-86755064.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-86341087.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-3449804.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-2766816.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-86486967.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-86705255.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-1er/ref-APM-86721061.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-15eme/ref-APM-87060605.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-2771802.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-87001072.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-85352054.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87033407.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-86135140.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-87002629.html</t>
+  </si>
+  <si>
+    <t>PARIS 9ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-9eme/ref-APM-86760401.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-3706435.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-87043901.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-84238457.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-85412408.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-85840286.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-7267702.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-7eme/ref-APM-7932449.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-15eme/ref-APM-83627769.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-84198668.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86961630.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-82703857.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-87007925.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-85559098.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-85291526.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86938200.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-17eme/ref-APM-86114542.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-10eme/ref-APM-2765808.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-8eme/ref-APM-83635347.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-86659415.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-16eme/ref-APM-3208344.html</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-6eme/ref-APM-86729411.html</t>
+  </si>
+  <si>
+    <t>PARIS 11ÈME</t>
+  </si>
+  <si>
+    <t>https://www.barnes-international.com/en/for-rent/france/paris-11eme/ref-APM-86050237.html</t>
+  </si>
+  <si>
+    <t>SeLoger</t>
+  </si>
+  <si>
+    <t>Paris 15ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273206899.htm</t>
+  </si>
+  <si>
+    <t>Paris 19ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273933589.htm</t>
+  </si>
+  <si>
+    <t>Paris 17ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273678077.htm</t>
+  </si>
+  <si>
+    <t>Paris 6ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/rennes/272330823.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273866199.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/violet-commerce/273849353.htm</t>
+  </si>
+  <si>
+    <t>Paris 16ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273834289.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/272541147.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273302365.htm</t>
+  </si>
+  <si>
+    <t>1 / 20</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/neuilly-sur-seine-92/ile-de-la-jatte-parc-d-orleans/273315131.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273864065.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639859.htm</t>
+  </si>
+  <si>
+    <t>Paris 18ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273307251.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639863.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273923913.htm</t>
+  </si>
+  <si>
+    <t>Paris 7ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-7eme-75/gros-caillou/273374159.htm</t>
+  </si>
+  <si>
+    <t>Paris 4ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273864063.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-18eme-75/montmartre/273396287.htm</t>
+  </si>
+  <si>
+    <t>Paris 10ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274057719.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/vaugirard-parc-des-expositions/271629933.htm</t>
+  </si>
+  <si>
+    <t>Paris 3ème</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273490291.htm</t>
+  </si>
+  <si>
+    <t>Nouveau</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/saint-ouen-93/marie-godillot-landy/273787275.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639889.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-17eme-75/ternes-maillot/273186559.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-18eme-75/goutte-d-or-chateau-rouge/274249093.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/273639857.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/pasteur-montparnasse/271456951.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639893.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630973.htm</t>
+  </si>
+  <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 06/07/2026, 01:55:16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barnes: FAILED — Failed to launch the browser process!
-[2363:2363:0706/015516.218981:FATAL:zygote_host_impl_linux.cc(128)] No usable sandbox! If you are running on Ubuntu 23.10+ or another Linux distro that has disabled unprivileged user namespaces with AppArmor, see https://chromium.googlesource.com/chromium/src/+/main/docs/security/apparmor-userns-restrictions.md. Otherwise see https://chromium.googlesource.com/chromium/src/+/main/docs/linux/suid_sandbox_development.md for more information on developing with the (older) SUID sandbox. If you want to live dangerously and need an immediate workaround, you can try using --no-sandbox.
-[0706/015516.227327:ERROR:file_io_posix.cc(145)] open /sys/devices/system/cpu/cpu0/cpufreq/scaling_cur_freq: No such file or directory (2)
-[0706/015516.227373:ERROR:file_io_posix.cc(145)] open /sys/devices/system/cpu/cpu0/cpufreq/scaling_max_freq: No such file or directory (2)
-TROUBLESHOOTING: https://pptr.dev/troubleshooting
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeLoger: FAILED — Failed to launch the browser process!
-[2380:2380:0706/015516.453032:FATAL:zygote_host_impl_linux.cc(128)] No usable sandbox! If you are running on Ubuntu 23.10+ or another Linux distro that has disabled unprivileged user namespaces with AppArmor, see https://chromium.googlesource.com/chromium/src/+/main/docs/security/apparmor-userns-restrictions.md. Otherwise see https://chromium.googlesource.com/chromium/src/+/main/docs/linux/suid_sandbox_development.md for more information on developing with the (older) SUID sandbox. If you want to live dangerously and need an immediate workaround, you can try using --no-sandbox.
-[0706/015516.460900:ERROR:file_io_posix.cc(145)] open /sys/devices/system/cpu/cpu0/cpufreq/scaling_cur_freq: No such file or directory (2)
-[0706/015516.460950:ERROR:file_io_posix.cc(145)] open /sys/devices/system/cpu/cpu0/cpufreq/scaling_max_freq: No such file or directory (2)
-TROUBLESHOOTING: https://pptr.dev/troubleshooting
-</t>
+    <t>Generated: 06/07/2026, 21:53:26</t>
+  </si>
+  <si>
+    <t>Barnes: 100 listings</t>
+  </si>
+  <si>
+    <t>SeLoger: 30 listings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot; €&quot;"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -79,15 +555,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFCC0000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -116,11 +592,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -462,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -494,6 +972,2988 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4">
+        <v>17000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3">
+        <v>256</v>
+      </c>
+      <c r="E2" s="5">
+        <f>B2/D2</f>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>170</v>
+      </c>
+      <c r="E3" s="5">
+        <f>B3/D3</f>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8700</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3">
+        <v>276</v>
+      </c>
+      <c r="E4" s="5">
+        <f>B4/D4</f>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6765</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>116</v>
+      </c>
+      <c r="E5" s="5">
+        <f>B5/D5</f>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6700</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>157</v>
+      </c>
+      <c r="E6" s="5">
+        <f>B6/D6</f>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4">
+        <v>6500</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>92</v>
+      </c>
+      <c r="E7" s="5">
+        <f>B7/D7</f>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>5500</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>152</v>
+      </c>
+      <c r="E8" s="5">
+        <f>B8/D8</f>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5200</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>96</v>
+      </c>
+      <c r="E9" s="5">
+        <f>B9/D9</f>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>70</v>
+      </c>
+      <c r="E10" s="5">
+        <f>B10/D10</f>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4">
+        <v>4200</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>89</v>
+      </c>
+      <c r="E11" s="5">
+        <f>B11/D11</f>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4">
+        <v>4200</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>82</v>
+      </c>
+      <c r="E12" s="5">
+        <f>B12/D12</f>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3800</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>63</v>
+      </c>
+      <c r="E13" s="5">
+        <f>B13/D13</f>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3500</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5">
+        <f>B14/D14</f>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3500</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>49</v>
+      </c>
+      <c r="E15" s="5">
+        <f>B15/D15</f>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3500</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5">
+        <f>B16/D16</f>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3490</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5">
+        <f>B17/D17</f>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="4">
+        <v>3300</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>77</v>
+      </c>
+      <c r="E18" s="5">
+        <f>B18/D18</f>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="4">
+        <v>3200</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3">
+        <v>67</v>
+      </c>
+      <c r="E19" s="5">
+        <f>B19/D19</f>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3100</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>63</v>
+      </c>
+      <c r="E20" s="5">
+        <f>B20/D20</f>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2830</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>101</v>
+      </c>
+      <c r="E21" s="5">
+        <f>B21/D21</f>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2600</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>66</v>
+      </c>
+      <c r="E22" s="5">
+        <f>B22/D22</f>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2580</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>66</v>
+      </c>
+      <c r="E23" s="5">
+        <f>B23/D23</f>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2500</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>64</v>
+      </c>
+      <c r="E24" s="5">
+        <f>B24/D24</f>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2400</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3">
+        <v>65</v>
+      </c>
+      <c r="E25" s="5">
+        <f>B25/D25</f>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2200</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>40</v>
+      </c>
+      <c r="E26" s="5">
+        <f>B26/D26</f>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1000</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3">
+        <v>17</v>
+      </c>
+      <c r="E27" s="5">
+        <f>B27/D27</f>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="4">
+        <v>50000</v>
+      </c>
+      <c r="C28" s="3">
+        <v>4</v>
+      </c>
+      <c r="D28" s="3">
+        <v>197</v>
+      </c>
+      <c r="E28" s="5">
+        <f>B28/D28</f>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="4">
+        <v>45000</v>
+      </c>
+      <c r="C29" s="3">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>321</v>
+      </c>
+      <c r="E29" s="5">
+        <f>B29/D29</f>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="4">
+        <v>25000</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3</v>
+      </c>
+      <c r="D30" s="3">
+        <v>185</v>
+      </c>
+      <c r="E30" s="5">
+        <f>B30/D30</f>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="4">
+        <v>25000</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3</v>
+      </c>
+      <c r="D31" s="3">
+        <v>289</v>
+      </c>
+      <c r="E31" s="5">
+        <f>B31/D31</f>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="4">
+        <v>20700</v>
+      </c>
+      <c r="C32" s="3">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="5">
+        <f>B32/D32</f>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="4">
+        <v>19500</v>
+      </c>
+      <c r="C33" s="3">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3">
+        <v>198</v>
+      </c>
+      <c r="E33" s="5">
+        <f>B33/D33</f>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="4">
+        <v>18450</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3">
+        <v>179</v>
+      </c>
+      <c r="E34" s="5">
+        <f>B34/D34</f>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="4">
+        <v>18000</v>
+      </c>
+      <c r="C35" s="3">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3">
+        <v>338</v>
+      </c>
+      <c r="E35" s="5">
+        <f>B35/D35</f>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="4">
+        <v>18000</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3">
+        <v>294</v>
+      </c>
+      <c r="E36" s="5">
+        <f>B36/D36</f>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="4">
+        <v>17000</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>315</v>
+      </c>
+      <c r="E37" s="5">
+        <f>B37/D37</f>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="4">
+        <v>15450</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3">
+        <v>179</v>
+      </c>
+      <c r="E38" s="5">
+        <f>B38/D38</f>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="4">
+        <v>15065</v>
+      </c>
+      <c r="C39" s="3">
+        <v>4</v>
+      </c>
+      <c r="D39" s="3">
+        <v>202</v>
+      </c>
+      <c r="E39" s="5">
+        <f>B39/D39</f>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="4">
+        <v>15000</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3">
+        <v>120</v>
+      </c>
+      <c r="E40" s="5">
+        <f>B40/D40</f>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="4">
+        <v>14800</v>
+      </c>
+      <c r="C41" s="3">
+        <v>4</v>
+      </c>
+      <c r="D41" s="3">
+        <v>166</v>
+      </c>
+      <c r="E41" s="5">
+        <f>B41/D41</f>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="4">
+        <v>14265</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3</v>
+      </c>
+      <c r="D42" s="3">
+        <v>360</v>
+      </c>
+      <c r="E42" s="5">
+        <f>B42/D42</f>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="4">
+        <v>13690</v>
+      </c>
+      <c r="C43" s="3">
+        <v>4</v>
+      </c>
+      <c r="D43" s="3">
+        <v>233</v>
+      </c>
+      <c r="E43" s="5">
+        <f>B43/D43</f>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="4">
+        <v>13000</v>
+      </c>
+      <c r="C44" s="3">
+        <v>4</v>
+      </c>
+      <c r="D44" s="3">
+        <v>228</v>
+      </c>
+      <c r="E44" s="5">
+        <f>B44/D44</f>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="4">
+        <v>12500</v>
+      </c>
+      <c r="C45" s="3">
+        <v>5</v>
+      </c>
+      <c r="D45" s="3">
+        <v>246</v>
+      </c>
+      <c r="E45" s="5">
+        <f>B45/D45</f>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C46" s="3">
+        <v>4</v>
+      </c>
+      <c r="D46" s="3">
+        <v>226</v>
+      </c>
+      <c r="E46" s="5">
+        <f>B46/D46</f>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C47" s="3">
+        <v>5</v>
+      </c>
+      <c r="D47" s="3">
+        <v>299</v>
+      </c>
+      <c r="E47" s="5">
+        <f>B47/D47</f>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C48" s="3">
+        <v>4</v>
+      </c>
+      <c r="D48" s="3">
+        <v>232</v>
+      </c>
+      <c r="E48" s="5">
+        <f>B48/D48</f>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="4">
+        <v>11548</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3">
+        <v>216</v>
+      </c>
+      <c r="E49" s="5">
+        <f>B49/D49</f>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="4">
+        <v>11520</v>
+      </c>
+      <c r="C50" s="3">
+        <v>4</v>
+      </c>
+      <c r="D50" s="3">
+        <v>220</v>
+      </c>
+      <c r="E50" s="5">
+        <f>B50/D50</f>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="4">
+        <v>11500</v>
+      </c>
+      <c r="C51" s="3">
+        <v>3</v>
+      </c>
+      <c r="D51" s="3">
+        <v>217</v>
+      </c>
+      <c r="E51" s="5">
+        <f>B51/D51</f>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="4">
+        <v>11500</v>
+      </c>
+      <c r="C52" s="3">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3">
+        <v>242</v>
+      </c>
+      <c r="E52" s="5">
+        <f>B52/D52</f>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="4">
+        <v>10600</v>
+      </c>
+      <c r="C53" s="3">
+        <v>4</v>
+      </c>
+      <c r="D53" s="3">
+        <v>214</v>
+      </c>
+      <c r="E53" s="5">
+        <f>B53/D53</f>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="4">
+        <v>10450</v>
+      </c>
+      <c r="C54" s="3">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3">
+        <v>156</v>
+      </c>
+      <c r="E54" s="5">
+        <f>B54/D54</f>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C55" s="3">
+        <v>5</v>
+      </c>
+      <c r="D55" s="3">
+        <v>220</v>
+      </c>
+      <c r="E55" s="5">
+        <f>B55/D55</f>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C56" s="3">
+        <v>3</v>
+      </c>
+      <c r="D56" s="3">
+        <v>153</v>
+      </c>
+      <c r="E56" s="5">
+        <f>B56/D56</f>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C57" s="3">
+        <v>3</v>
+      </c>
+      <c r="D57" s="3">
+        <v>188</v>
+      </c>
+      <c r="E57" s="5">
+        <f>B57/D57</f>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="4">
+        <v>9900</v>
+      </c>
+      <c r="C58" s="3">
+        <v>4</v>
+      </c>
+      <c r="D58" s="3">
+        <v>146</v>
+      </c>
+      <c r="E58" s="5">
+        <f>B58/D58</f>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="4">
+        <v>9800</v>
+      </c>
+      <c r="C59" s="3">
+        <v>3</v>
+      </c>
+      <c r="D59" s="3">
+        <v>241</v>
+      </c>
+      <c r="E59" s="5">
+        <f>B59/D59</f>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="4">
+        <v>9000</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3">
+        <v>163</v>
+      </c>
+      <c r="E60" s="5">
+        <f>B60/D60</f>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="4">
+        <v>8900</v>
+      </c>
+      <c r="C61" s="3">
+        <v>3</v>
+      </c>
+      <c r="D61" s="3">
+        <v>152</v>
+      </c>
+      <c r="E61" s="5">
+        <f>B61/D61</f>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="4">
+        <v>8700</v>
+      </c>
+      <c r="C62" s="3">
+        <v>3</v>
+      </c>
+      <c r="D62" s="3">
+        <v>104</v>
+      </c>
+      <c r="E62" s="5">
+        <f>B62/D62</f>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="4">
+        <v>8500</v>
+      </c>
+      <c r="C63" s="3">
+        <v>3</v>
+      </c>
+      <c r="D63" s="3">
+        <v>153</v>
+      </c>
+      <c r="E63" s="5">
+        <f>B63/D63</f>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="4">
+        <v>8500</v>
+      </c>
+      <c r="C64" s="3">
+        <v>5</v>
+      </c>
+      <c r="D64" s="3">
+        <v>231</v>
+      </c>
+      <c r="E64" s="5">
+        <f>B64/D64</f>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="4">
+        <v>8400</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3</v>
+      </c>
+      <c r="D65" s="3">
+        <v>238</v>
+      </c>
+      <c r="E65" s="5">
+        <f>B65/D65</f>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C66" s="3">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3">
+        <v>193</v>
+      </c>
+      <c r="E66" s="5">
+        <f>B66/D66</f>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="4">
+        <v>7800</v>
+      </c>
+      <c r="C67" s="3">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3">
+        <v>242</v>
+      </c>
+      <c r="E67" s="5">
+        <f>B67/D67</f>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="4">
+        <v>7500</v>
+      </c>
+      <c r="C68" s="3">
+        <v>4</v>
+      </c>
+      <c r="D68" s="3">
+        <v>205</v>
+      </c>
+      <c r="E68" s="5">
+        <f>B68/D68</f>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="4">
+        <v>7400</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3</v>
+      </c>
+      <c r="D69" s="3">
+        <v>166</v>
+      </c>
+      <c r="E69" s="5">
+        <f>B69/D69</f>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="4">
+        <v>7000</v>
+      </c>
+      <c r="C70" s="3">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3">
+        <v>81</v>
+      </c>
+      <c r="E70" s="5">
+        <f>B70/D70</f>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="4">
+        <v>6950</v>
+      </c>
+      <c r="C71" s="3">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3">
+        <v>109</v>
+      </c>
+      <c r="E71" s="5">
+        <f>B71/D71</f>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="4">
+        <v>6765</v>
+      </c>
+      <c r="C72" s="3">
+        <v>4</v>
+      </c>
+      <c r="D72" s="3">
+        <v>116</v>
+      </c>
+      <c r="E72" s="5">
+        <f>B72/D72</f>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="4">
+        <v>6550</v>
+      </c>
+      <c r="C73" s="3">
+        <v>3</v>
+      </c>
+      <c r="D73" s="3">
+        <v>146</v>
+      </c>
+      <c r="E73" s="5">
+        <f>B73/D73</f>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="4">
+        <v>6520</v>
+      </c>
+      <c r="C74" s="3">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3">
+        <v>124</v>
+      </c>
+      <c r="E74" s="5">
+        <f>B74/D74</f>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="4">
+        <v>6500</v>
+      </c>
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+      <c r="D75" s="3">
+        <v>152</v>
+      </c>
+      <c r="E75" s="5">
+        <f>B75/D75</f>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="4">
+        <v>6500</v>
+      </c>
+      <c r="C76" s="3">
+        <v>3</v>
+      </c>
+      <c r="D76" s="3">
+        <v>125</v>
+      </c>
+      <c r="E76" s="5">
+        <f>B76/D76</f>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="4">
+        <v>6500</v>
+      </c>
+      <c r="C77" s="3">
+        <v>3</v>
+      </c>
+      <c r="D77" s="3">
+        <v>115</v>
+      </c>
+      <c r="E77" s="5">
+        <f>B77/D77</f>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="4">
+        <v>6000</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3">
+        <v>52</v>
+      </c>
+      <c r="E78" s="5">
+        <f>B78/D78</f>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="4">
+        <v>5800</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3">
+        <v>105</v>
+      </c>
+      <c r="E79" s="5">
+        <f>B79/D79</f>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="4">
+        <v>5500</v>
+      </c>
+      <c r="C80" s="3">
+        <v>3</v>
+      </c>
+      <c r="D80" s="3">
+        <v>152</v>
+      </c>
+      <c r="E80" s="5">
+        <f>B80/D80</f>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="4">
+        <v>5500</v>
+      </c>
+      <c r="C81" s="3">
+        <v>3</v>
+      </c>
+      <c r="D81" s="3">
+        <v>129</v>
+      </c>
+      <c r="E81" s="5">
+        <f>B81/D81</f>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="4">
+        <v>5500</v>
+      </c>
+      <c r="C82" s="3">
+        <v>2</v>
+      </c>
+      <c r="D82" s="3">
+        <v>105</v>
+      </c>
+      <c r="E82" s="5">
+        <f>B82/D82</f>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="4">
+        <v>5500</v>
+      </c>
+      <c r="C83" s="3">
+        <v>3</v>
+      </c>
+      <c r="D83" s="3">
+        <v>129</v>
+      </c>
+      <c r="E83" s="5">
+        <f>B83/D83</f>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="4">
+        <v>5400</v>
+      </c>
+      <c r="C84" s="3">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3">
+        <v>91</v>
+      </c>
+      <c r="E84" s="5">
+        <f>B84/D84</f>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="4">
+        <v>5200</v>
+      </c>
+      <c r="C85" s="3">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3">
+        <v>90</v>
+      </c>
+      <c r="E85" s="5">
+        <f>B85/D85</f>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="4">
+        <v>5150</v>
+      </c>
+      <c r="C86" s="3">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3">
+        <v>137</v>
+      </c>
+      <c r="E86" s="5">
+        <f>B86/D86</f>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="4">
+        <v>5073</v>
+      </c>
+      <c r="C87" s="3">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3">
+        <v>136</v>
+      </c>
+      <c r="E87" s="5">
+        <f>B87/D87</f>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="4">
+        <v>4900</v>
+      </c>
+      <c r="C88" s="3">
+        <v>2</v>
+      </c>
+      <c r="D88" s="3">
+        <v>84</v>
+      </c>
+      <c r="E88" s="5">
+        <f>B88/D88</f>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="4">
+        <v>4800</v>
+      </c>
+      <c r="C89" s="3">
+        <v>3</v>
+      </c>
+      <c r="D89" s="3">
+        <v>127</v>
+      </c>
+      <c r="E89" s="5">
+        <f>B89/D89</f>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="4">
+        <v>4800</v>
+      </c>
+      <c r="C90" s="3">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3">
+        <v>127</v>
+      </c>
+      <c r="E90" s="5">
+        <f>B90/D90</f>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="4">
+        <v>4800</v>
+      </c>
+      <c r="C91" s="3">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3">
+        <v>117</v>
+      </c>
+      <c r="E91" s="5">
+        <f>B91/D91</f>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="4">
+        <v>4800</v>
+      </c>
+      <c r="C92" s="3">
+        <v>3</v>
+      </c>
+      <c r="D92" s="3">
+        <v>145</v>
+      </c>
+      <c r="E92" s="5">
+        <f>B92/D92</f>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="4">
+        <v>4500</v>
+      </c>
+      <c r="C93" s="3">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3">
+        <v>137</v>
+      </c>
+      <c r="E93" s="5">
+        <f>B93/D93</f>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="4">
+        <v>4400</v>
+      </c>
+      <c r="C94" s="3">
+        <v>3</v>
+      </c>
+      <c r="D94" s="3">
+        <v>104</v>
+      </c>
+      <c r="E94" s="5">
+        <f>B94/D94</f>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="4">
+        <v>4200</v>
+      </c>
+      <c r="C95" s="3">
+        <v>3</v>
+      </c>
+      <c r="D95" s="3">
+        <v>103</v>
+      </c>
+      <c r="E95" s="5">
+        <f>B95/D95</f>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="4">
+        <v>4053</v>
+      </c>
+      <c r="C96" s="3">
+        <v>3</v>
+      </c>
+      <c r="D96" s="3">
+        <v>140</v>
+      </c>
+      <c r="E96" s="5">
+        <f>B96/D96</f>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="4">
+        <v>3900</v>
+      </c>
+      <c r="C97" s="3">
+        <v>1</v>
+      </c>
+      <c r="D97" s="3">
+        <v>68</v>
+      </c>
+      <c r="E97" s="5">
+        <f>B97/D97</f>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" s="4">
+        <v>3900</v>
+      </c>
+      <c r="C98" s="3">
+        <v>2</v>
+      </c>
+      <c r="D98" s="3">
+        <v>96</v>
+      </c>
+      <c r="E98" s="5">
+        <f>B98/D98</f>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="4">
+        <v>3850</v>
+      </c>
+      <c r="C99" s="3">
+        <v>3</v>
+      </c>
+      <c r="D99" s="3">
+        <v>124</v>
+      </c>
+      <c r="E99" s="5">
+        <f>B99/D99</f>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" s="4">
+        <v>3750</v>
+      </c>
+      <c r="C100" s="3">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3">
+        <v>86</v>
+      </c>
+      <c r="E100" s="5">
+        <f>B100/D100</f>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" s="4">
+        <v>3500</v>
+      </c>
+      <c r="C101" s="3">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3">
+        <v>101</v>
+      </c>
+      <c r="E101" s="5">
+        <f>B101/D101</f>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B102" s="4">
+        <v>2200</v>
+      </c>
+      <c r="C102" s="3">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3">
+        <v>53</v>
+      </c>
+      <c r="E102" s="5">
+        <f>B102/D102</f>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B103" s="4">
+        <v>800</v>
+      </c>
+      <c r="C103" s="3">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3">
+        <v>43</v>
+      </c>
+      <c r="E103" s="5">
+        <f>B103/D103</f>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B104" s="4">
+        <v>7900</v>
+      </c>
+      <c r="C104" s="3">
+        <v>4</v>
+      </c>
+      <c r="D104" s="3">
+        <v>127</v>
+      </c>
+      <c r="E104" s="5">
+        <f>B104/D104</f>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B105" s="4">
+        <v>6330</v>
+      </c>
+      <c r="C105" s="3">
+        <v>3</v>
+      </c>
+      <c r="D105" s="3">
+        <v>98</v>
+      </c>
+      <c r="E105" s="5">
+        <f>B105/D105</f>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106" s="4">
+        <v>4700</v>
+      </c>
+      <c r="C106" s="3">
+        <v>5</v>
+      </c>
+      <c r="D106" s="3">
+        <v>107</v>
+      </c>
+      <c r="E106" s="5">
+        <f>B106/D106</f>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B107" s="4">
+        <v>2710</v>
+      </c>
+      <c r="C107" s="3">
+        <v>3</v>
+      </c>
+      <c r="D107" s="3">
+        <v>47</v>
+      </c>
+      <c r="E107" s="5">
+        <f>B107/D107</f>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B108" s="4">
+        <v>4250</v>
+      </c>
+      <c r="C108" s="3">
+        <v>6</v>
+      </c>
+      <c r="D108" s="3">
+        <v>116.8</v>
+      </c>
+      <c r="E108" s="5">
+        <f>B108/D108</f>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B109" s="4">
+        <v>2250</v>
+      </c>
+      <c r="C109" s="3">
+        <v>2</v>
+      </c>
+      <c r="D109" s="3">
+        <v>52</v>
+      </c>
+      <c r="E109" s="5">
+        <f>B109/D109</f>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B110" s="4">
+        <v>4150</v>
+      </c>
+      <c r="C110" s="3">
+        <v>4</v>
+      </c>
+      <c r="D110" s="3">
+        <v>109</v>
+      </c>
+      <c r="E110" s="5">
+        <f>B110/D110</f>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" s="4">
+        <v>2850</v>
+      </c>
+      <c r="C111" s="3">
+        <v>3</v>
+      </c>
+      <c r="D111" s="3">
+        <v>84</v>
+      </c>
+      <c r="E111" s="5">
+        <f>B111/D111</f>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B112" s="4">
+        <v>1890</v>
+      </c>
+      <c r="C112" s="3">
+        <v>2</v>
+      </c>
+      <c r="D112" s="3">
+        <v>38</v>
+      </c>
+      <c r="E112" s="5">
+        <f>B112/D112</f>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B113" s="4">
+        <v>1100</v>
+      </c>
+      <c r="C113" s="3">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="E113" s="5">
+        <f>B113/D113</f>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114" s="4">
+        <v>2100</v>
+      </c>
+      <c r="C114" s="3">
+        <v>2</v>
+      </c>
+      <c r="D114" s="3">
+        <v>57</v>
+      </c>
+      <c r="E114" s="5">
+        <f>B114/D114</f>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B115" s="4">
+        <v>1100</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3">
+        <v>10.7</v>
+      </c>
+      <c r="E115" s="5">
+        <f>B115/D115</f>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" s="4">
+        <v>1603</v>
+      </c>
+      <c r="C116" s="3">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3">
+        <v>48</v>
+      </c>
+      <c r="E116" s="5">
+        <f>B116/D116</f>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="4">
+        <v>162180</v>
+      </c>
+      <c r="C117" s="3">
+        <v>2</v>
+      </c>
+      <c r="D117" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="E117" s="5">
+        <f>B117/D117</f>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="4">
+        <v>1500</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3">
+        <v>18</v>
+      </c>
+      <c r="E118" s="5">
+        <f>B118/D118</f>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="4">
+        <v>3650</v>
+      </c>
+      <c r="C119" s="3">
+        <v>4</v>
+      </c>
+      <c r="D119" s="3">
+        <v>100</v>
+      </c>
+      <c r="E119" s="5">
+        <f>B119/D119</f>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="4">
+        <v>7250</v>
+      </c>
+      <c r="C120" s="3">
+        <v>6</v>
+      </c>
+      <c r="D120" s="3">
+        <v>197</v>
+      </c>
+      <c r="E120" s="5">
+        <f>B120/D120</f>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" s="4">
+        <v>1420</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3">
+        <v>37</v>
+      </c>
+      <c r="E121" s="5">
+        <f>B121/D121</f>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="4">
+        <v>8900</v>
+      </c>
+      <c r="C122" s="3">
+        <v>4</v>
+      </c>
+      <c r="D122" s="3">
+        <v>151</v>
+      </c>
+      <c r="E122" s="5">
+        <f>B122/D122</f>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B123" s="4">
+        <v>680</v>
+      </c>
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3">
+        <v>22</v>
+      </c>
+      <c r="E123" s="5">
+        <f>B123/D123</f>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="4">
+        <v>1100</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="E124" s="5">
+        <f>B124/D124</f>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" s="4">
+        <v>2850</v>
+      </c>
+      <c r="C125" s="3">
+        <v>2</v>
+      </c>
+      <c r="D125" s="3">
+        <v>80</v>
+      </c>
+      <c r="E125" s="5">
+        <f>B125/D125</f>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4">
+        <v>1175</v>
+      </c>
+      <c r="C126" s="3">
+        <v>2</v>
+      </c>
+      <c r="D126" s="3">
+        <v>33</v>
+      </c>
+      <c r="E126" s="5">
+        <f>B126/D126</f>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4">
+        <v>1200</v>
+      </c>
+      <c r="C127" s="3">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="E127" s="5">
+        <f>B127/D127</f>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B128" s="4">
+        <v>1200</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3">
+        <v>13.6</v>
+      </c>
+      <c r="E128" s="5">
+        <f>B128/D128</f>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B129" s="4">
+        <v>1850</v>
+      </c>
+      <c r="C129" s="3">
+        <v>2</v>
+      </c>
+      <c r="D129" s="3">
+        <v>43</v>
+      </c>
+      <c r="E129" s="5">
+        <f>B129/D129</f>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B130" s="4">
+        <v>1255</v>
+      </c>
+      <c r="C130" s="3">
+        <v>1</v>
+      </c>
+      <c r="D130" s="3">
+        <v>15.3</v>
+      </c>
+      <c r="E130" s="5">
+        <f>B130/D130</f>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B131" s="4">
+        <v>1205</v>
+      </c>
+      <c r="C131" s="3">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3">
+        <v>14</v>
+      </c>
+      <c r="E131" s="5">
+        <f>B131/D131</f>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -512,23 +3972,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
+      <c r="A1" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
+      <c r="A2" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
+      <c r="A3" s="7" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>10</v>
+      <c r="A4" s="7" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="472">
   <si>
     <t>Source</t>
   </si>
@@ -737,10 +737,10 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/rennes/272330823.htm</t>
   </si>
   <si>
-    <t>YFRI pour CSO</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/273555395.htm</t>
+    <t>charges comprises</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/saint-ouen-93/271170371.htm</t>
   </si>
   <si>
     <t>Paris 18ème</t>
@@ -779,15 +779,15 @@
     <t>https://www.seloger.com/annonces/locations/appartement/paris-7eme-75/ecole-militaire/274381299.htm</t>
   </si>
   <si>
-    <t>1 / 10</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/saint-denis-93/delaunay-belleville/274249075.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273630989.htm</t>
   </si>
   <si>
+    <t>1 / 29</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/neuilly-sur-seine-92/ile-de-la-jatte-parc-d-orleans/255050063.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273639893.htm</t>
   </si>
   <si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/alleray-procession/270367951.htm</t>
+  </si>
+  <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/auteuil-nord/273630981.htm</t>
   </si>
   <si>
     <t>Book-a-Flat</t>
@@ -1038,6 +1041,9 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/273555397.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/273555395.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/270298401.htm</t>
   </si>
   <si>
@@ -1047,7 +1053,7 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/270998099.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/dupleix-motte-picquet/270203429.htm</t>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-7eme-75/gros-caillou/268989177.htm</t>
   </si>
   <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/parchamp-albert-kahn/268308221.htm</t>
@@ -1071,12 +1077,12 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/prince-marmottan/273738799.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/274786855.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/274005401.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/274786855.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/silly-gallieni/274832065.htm</t>
   </si>
   <si>
@@ -1086,6 +1092,9 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/vaillant-sembat/274773159.htm</t>
   </si>
   <si>
+    <t>https://www.seloger.com/annonces/locations/appartement/paris-16eme-75/chaillot/269929907.htm</t>
+  </si>
+  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/vaillant-sembat/272325469.htm</t>
   </si>
   <si>
@@ -1110,102 +1119,6 @@
     <t>https://www.seloger.com/annonces/locations/appartement/boulogne-billancourt-92/reine-mairie/273705839.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/273842041.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/264422657.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274796827.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274647305.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274456853.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/274411689.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/la-verboise/274572509.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/273650489.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/mairie/274724371.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/saint-cloud-92/montretout/274045583.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687835.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/levallois-perret-92/georges-pompidou/273688395.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273688087.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687001.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687923.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687457.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687965.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/courbevoie-92/gambetta/273687845.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687773.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687087.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687463.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687359.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687915.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/rueil-malmaison-92/rueil-sur-seine-plaine-gare/274819647.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273686995.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/clichy-92/entree-de-ville/273608851.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687861.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273688091.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/clichy-92/centre-ville/273687807.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687905.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/garches-92/273687921.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/asnieres-sur-seine-92/bac-becon-flachat-colombes/273687675.htm</t>
-  </si>
-  <si>
     <t>https://www.seloger.com/annonces/locations/appartement/le-vesinet-78/centre/273936385.htm</t>
   </si>
   <si>
@@ -1392,76 +1305,10 @@
     <t>https://www.seloger.com/annonces/locations/appartement/saint-germain-en-laye-78/armagis/273546285.htm</t>
   </si>
   <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-germain-des-pres/241342323.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/274576347.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-placide/274578193.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/274575585.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/notre-dame-des-champs/274576073.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274577585.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274606679.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/268322589.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/monnaie/264585199.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/176042961.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/268317627.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/249315871.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-germain-des-pres/238478807.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/saint-placide/274722185.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/rennes/273957065.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-15eme-75/cambronne-garibaldi/271674939.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274081961.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/274712487.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/odeon/272282681.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/274588633.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-75/273754065.htm</t>
-  </si>
-  <si>
-    <t>https://www.seloger.com/annonces/locations/appartement/paris-6eme-75/notre-dame-des-champs/273467065.htm</t>
-  </si>
-  <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 13/07/2026, 15:04:48</t>
+    <t>Generated: 13/07/2026, 15:26:51</t>
   </si>
   <si>
     <t>Barnes: 100 listings</t>
@@ -1473,7 +1320,7 @@
     <t>Junot: 17 listings</t>
   </si>
   <si>
-    <t>SeLoger: 26 listings</t>
+    <t>SeLoger: 27 listings</t>
   </si>
   <si>
     <t>SeLoger-Suburbs: FAILED — Timed out after 300000ms: SeLoger-Suburbs scrape</t>
@@ -1485,10 +1332,10 @@
     <t>Perenium: 13 listings</t>
   </si>
   <si>
-    <t>SeLoger-Suburb-boulogne-billancourt: 29 listings</t>
-  </si>
-  <si>
-    <t>SeLoger-Suburb-garches: 32 listings</t>
+    <t>SeLoger-Suburb-boulogne-billancourt: 31 listings</t>
+  </si>
+  <si>
+    <t>SeLoger-Suburb-garches: 0 listings</t>
   </si>
   <si>
     <t>SeLoger-Suburb-le-vesinet: 31 listings</t>
@@ -1572,7 +1419,7 @@
     <t>SeLoger-Paris-5e: 0 listings</t>
   </si>
   <si>
-    <t>SeLoger-Paris-6e: 22 listings</t>
+    <t>SeLoger-Paris-6e: 0 listings</t>
   </si>
   <si>
     <t>SeLoger-Paris-7e: 0 listings</t>
@@ -1994,7 +1841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K386"/>
+  <dimension ref="A1:K335"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8214,16 +8061,16 @@
         <v>227</v>
       </c>
       <c r="B180" s="3">
-        <v>899</v>
+        <v>696</v>
       </c>
       <c r="C180" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D180" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F180" s="4">
         <f>B180/E180</f>
@@ -8238,7 +8085,7 @@
         <v>13</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K180" s="2" t="s">
         <v>242</v>
@@ -8564,34 +8411,34 @@
         <v>227</v>
       </c>
       <c r="B190" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C190" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" s="2">
         <v>1</v>
       </c>
       <c r="E190" s="2">
-        <v>51</v>
+        <v>12.3</v>
       </c>
       <c r="F190" s="4">
         <f>B190/E190</f>
       </c>
       <c r="G190" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K190" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J190" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K190" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="191" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8599,22 +8446,22 @@
         <v>227</v>
       </c>
       <c r="B191" s="3">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C191" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D191" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191" s="2">
-        <v>12.3</v>
+        <v>90</v>
       </c>
       <c r="F191" s="4">
         <f>B191/E191</f>
       </c>
       <c r="G191" s="2" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>13</v>
@@ -8623,7 +8470,7 @@
         <v>13</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K191" s="2" t="s">
         <v>257</v>
@@ -8836,56 +8683,58 @@
     </row>
     <row r="198" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="B198" s="3">
-        <v>50000</v>
+        <v>200</v>
       </c>
       <c r="C198" s="2">
-        <v>5</v>
-      </c>
-      <c r="D198" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="D198" s="2">
+        <v>2</v>
+      </c>
       <c r="E198" s="2">
-        <v>450</v>
+        <v>12.3</v>
       </c>
       <c r="F198" s="4">
         <f>B198/E198</f>
       </c>
       <c r="G198" s="2" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="199" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B199" s="3">
-        <v>18000</v>
+        <v>50000</v>
       </c>
       <c r="C199" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2">
-        <v>247</v>
+        <v>450</v>
       </c>
       <c r="F199" s="4">
         <f>B199/E199</f>
       </c>
       <c r="G199" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>21</v>
@@ -8902,155 +8751,155 @@
     </row>
     <row r="200" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B200" s="3">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="C200" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="F200" s="4">
         <f>B200/E200</f>
       </c>
       <c r="G200" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J200" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K200" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I200" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J200" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K200" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="201" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B201" s="3">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="C201" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="F201" s="4">
         <f>B201/E201</f>
       </c>
       <c r="G201" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J201" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K201" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I201" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J201" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K201" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B202" s="3">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="C202" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="F202" s="4">
         <f>B202/E202</f>
       </c>
       <c r="G202" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K202" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I202" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J202" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K202" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="203" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B203" s="3">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="C203" s="2">
         <v>3</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F203" s="4">
         <f>B203/E203</f>
       </c>
       <c r="G203" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K203" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I203" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J203" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K203" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="204" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B204" s="3">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="C204" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="F204" s="4">
         <f>B204/E204</f>
       </c>
       <c r="G204" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>21</v>
@@ -9067,56 +8916,56 @@
     </row>
     <row r="205" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B205" s="3">
-        <v>6300</v>
+        <v>9000</v>
       </c>
       <c r="C205" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F205" s="4">
         <f>B205/E205</f>
       </c>
       <c r="G205" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J205" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K205" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I205" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J205" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K205" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="206" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B206" s="3">
-        <v>5250</v>
+        <v>6300</v>
       </c>
       <c r="C206" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="F206" s="4">
         <f>B206/E206</f>
       </c>
       <c r="G206" s="2" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>21</v>
@@ -9133,56 +8982,56 @@
     </row>
     <row r="207" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B207" s="3">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="C207" s="2">
         <v>2</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F207" s="4">
         <f>B207/E207</f>
       </c>
       <c r="G207" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K207" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I207" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J207" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K207" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="208" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B208" s="3">
-        <v>4545</v>
+        <v>5200</v>
       </c>
       <c r="C208" s="2">
         <v>2</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F208" s="4">
         <f>B208/E208</f>
       </c>
       <c r="G208" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>21</v>
@@ -9199,56 +9048,56 @@
     </row>
     <row r="209" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B209" s="3">
-        <v>4300</v>
+        <v>4545</v>
       </c>
       <c r="C209" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="F209" s="4">
         <f>B209/E209</f>
       </c>
       <c r="G209" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K209" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I209" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J209" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K209" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="210" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B210" s="3">
-        <v>3950</v>
+        <v>4300</v>
       </c>
       <c r="C210" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F210" s="4">
         <f>B210/E210</f>
       </c>
       <c r="G210" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>21</v>
@@ -9265,23 +9114,23 @@
     </row>
     <row r="211" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B211" s="3">
-        <v>3800</v>
+        <v>3950</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F211" s="4">
         <f>B211/E211</f>
       </c>
       <c r="G211" s="2" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>21</v>
@@ -9298,89 +9147,89 @@
     </row>
     <row r="212" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B212" s="3">
-        <v>3750</v>
+        <v>3800</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F212" s="4">
         <f>B212/E212</f>
       </c>
       <c r="G212" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I212" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K212" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I212" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J212" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="213" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B213" s="3">
-        <v>3490</v>
+        <v>3750</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F213" s="4">
         <f>B213/E213</f>
       </c>
       <c r="G213" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I213" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K213" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I213" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J213" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K213" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="214" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B214" s="3">
-        <v>3300</v>
+        <v>3490</v>
       </c>
       <c r="C214" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F214" s="4">
         <f>B214/E214</f>
       </c>
       <c r="G214" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>21</v>
@@ -9397,56 +9246,56 @@
     </row>
     <row r="215" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B215" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="C215" s="2">
         <v>2</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F215" s="4">
         <f>B215/E215</f>
       </c>
       <c r="G215" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I215" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J215" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K215" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I215" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J215" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K215" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="216" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B216" s="3">
-        <v>2950</v>
+        <v>3200</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="F216" s="4">
         <f>B216/E216</f>
       </c>
       <c r="G216" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>21</v>
@@ -9463,23 +9312,23 @@
     </row>
     <row r="217" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B217" s="3">
-        <v>2800</v>
+        <v>2950</v>
       </c>
       <c r="C217" s="2">
         <v>1</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F217" s="4">
         <f>B217/E217</f>
       </c>
       <c r="G217" s="2" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>21</v>
@@ -9496,23 +9345,23 @@
     </row>
     <row r="218" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B218" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="C218" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F218" s="4">
         <f>B218/E218</f>
       </c>
       <c r="G218" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>21</v>
@@ -9529,23 +9378,23 @@
     </row>
     <row r="219" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B219" s="3">
-        <v>2610</v>
+        <v>2700</v>
       </c>
       <c r="C219" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F219" s="4">
         <f>B219/E219</f>
       </c>
       <c r="G219" s="2" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>21</v>
@@ -9562,23 +9411,23 @@
     </row>
     <row r="220" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B220" s="3">
-        <v>2550</v>
+        <v>2610</v>
       </c>
       <c r="C220" s="2">
         <v>1</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F220" s="4">
         <f>B220/E220</f>
       </c>
       <c r="G220" s="2" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>21</v>
@@ -9595,23 +9444,23 @@
     </row>
     <row r="221" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B221" s="3">
-        <v>2520</v>
+        <v>2550</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F221" s="4">
         <f>B221/E221</f>
       </c>
       <c r="G221" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>21</v>
@@ -9628,23 +9477,23 @@
     </row>
     <row r="222" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B222" s="3">
-        <v>2100</v>
+        <v>2520</v>
       </c>
       <c r="C222" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F222" s="4">
         <f>B222/E222</f>
       </c>
       <c r="G222" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>21</v>
@@ -9661,7 +9510,7 @@
     </row>
     <row r="223" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B223" s="3">
         <v>2100</v>
@@ -9671,13 +9520,13 @@
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="F223" s="4">
         <f>B223/E223</f>
       </c>
       <c r="G223" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>21</v>
@@ -9694,7 +9543,7 @@
     </row>
     <row r="224" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B224" s="3">
         <v>2100</v>
@@ -9704,46 +9553,46 @@
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F224" s="4">
         <f>B224/E224</f>
       </c>
       <c r="G224" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I224" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J224" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K224" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I224" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J224" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="225" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B225" s="3">
-        <v>1975</v>
+        <v>2100</v>
       </c>
       <c r="C225" s="2">
         <v>1</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F225" s="4">
         <f>B225/E225</f>
       </c>
       <c r="G225" s="2" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>21</v>
@@ -9760,23 +9609,23 @@
     </row>
     <row r="226" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B226" s="3">
-        <v>1961</v>
+        <v>1975</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F226" s="4">
         <f>B226/E226</f>
       </c>
       <c r="G226" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>21</v>
@@ -9793,54 +9642,56 @@
     </row>
     <row r="227" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B227" s="3">
-        <v>1950</v>
+        <v>1961</v>
       </c>
       <c r="C227" s="2">
         <v>1</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F227" s="4">
         <f>B227/E227</f>
       </c>
       <c r="G227" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I227" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J227" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K227" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I227" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J227" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K227" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="228" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B228" s="3">
-        <v>1415</v>
-      </c>
-      <c r="C228" s="2"/>
+        <v>1950</v>
+      </c>
+      <c r="C228" s="2">
+        <v>1</v>
+      </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F228" s="4">
         <f>B228/E228</f>
       </c>
       <c r="G228" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>21</v>
@@ -9857,52 +9708,52 @@
     </row>
     <row r="229" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B229" s="3">
-        <v>1131</v>
+        <v>1415</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F229" s="4">
         <f>B229/E229</f>
       </c>
       <c r="G229" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I229" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J229" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K229" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="H229" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I229" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J229" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K229" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="230" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="B230" s="3">
-        <v>825</v>
+        <v>1131</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2">
-        <v>17.13</v>
+        <v>16</v>
       </c>
       <c r="F230" s="4">
         <f>B230/E230</f>
       </c>
       <c r="G230" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>21</v>
@@ -9914,352 +9765,352 @@
         <v>21</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="231" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B231" s="3">
-        <v>500</v>
-      </c>
-      <c r="C231" s="2">
-        <v>2</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="2">
-        <v>542.59</v>
+        <v>17.13</v>
       </c>
       <c r="F231" s="4">
         <f>B231/E231</f>
       </c>
       <c r="G231" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I231" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J231" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K231" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="H231" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I231" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J231" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K231" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="232" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B232" s="3">
-        <v>636</v>
+        <v>500</v>
       </c>
       <c r="C232" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" s="2">
-        <v>102.1</v>
+        <v>542.59</v>
       </c>
       <c r="F232" s="4">
         <f>B232/E232</f>
       </c>
       <c r="G232" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J232" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K232" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I232" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J232" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K232" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="233" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B233" s="3">
-        <v>375</v>
+        <v>636</v>
       </c>
       <c r="C233" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2">
-        <v>87.1</v>
+        <v>102.1</v>
       </c>
       <c r="F233" s="4">
         <f>B233/E233</f>
       </c>
       <c r="G233" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I233" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J233" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K233" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I233" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J233" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K233" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="234" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B234" s="3">
-        <v>110</v>
-      </c>
-      <c r="C234" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="C234" s="2">
+        <v>4</v>
+      </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2">
-        <v>28.56</v>
+        <v>87.1</v>
       </c>
       <c r="F234" s="4">
         <f>B234/E234</f>
       </c>
       <c r="G234" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I234" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J234" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K234" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I234" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J234" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K234" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="235" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B235" s="3">
-        <v>700</v>
-      </c>
-      <c r="C235" s="2">
-        <v>4</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C235" s="2"/>
       <c r="D235" s="2"/>
       <c r="E235" s="2">
-        <v>98.3</v>
+        <v>28.56</v>
       </c>
       <c r="F235" s="4">
         <f>B235/E235</f>
       </c>
       <c r="G235" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I235" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J235" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K235" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I235" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J235" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K235" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="236" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B236" s="3">
-        <v>15</v>
-      </c>
-      <c r="C236" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="C236" s="2">
+        <v>4</v>
+      </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2">
-        <v>423.29</v>
+        <v>98.3</v>
       </c>
       <c r="F236" s="4">
         <f>B236/E236</f>
       </c>
       <c r="G236" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I236" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J236" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K236" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I236" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J236" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K236" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B237" s="3">
-        <v>356</v>
-      </c>
-      <c r="C237" s="2">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2">
-        <v>3131.63</v>
+        <v>423.29</v>
       </c>
       <c r="F237" s="4">
         <f>B237/E237</f>
       </c>
       <c r="G237" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I237" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J237" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K237" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I237" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J237" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K237" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B238" s="3">
-        <v>198</v>
+        <v>356</v>
       </c>
       <c r="C238" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2">
-        <v>40.54</v>
+        <v>3131.63</v>
       </c>
       <c r="F238" s="4">
         <f>B238/E238</f>
       </c>
       <c r="G238" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I238" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J238" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K238" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I238" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J238" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K238" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B239" s="3">
-        <v>330</v>
+        <v>198</v>
       </c>
       <c r="C239" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2">
-        <v>98.62</v>
+        <v>40.54</v>
       </c>
       <c r="F239" s="4">
         <f>B239/E239</f>
       </c>
       <c r="G239" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I239" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K239" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I239" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J239" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K239" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B240" s="3">
-        <v>650</v>
+        <v>330</v>
       </c>
       <c r="C240" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2">
-        <v>43.68</v>
+        <v>98.62</v>
       </c>
       <c r="F240" s="4">
         <f>B240/E240</f>
       </c>
       <c r="G240" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I240" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J240" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K240" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I240" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J240" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K240" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B241" s="3">
-        <v>875</v>
-      </c>
-      <c r="C241" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="C241" s="2">
+        <v>2</v>
+      </c>
       <c r="D241" s="2"/>
       <c r="E241" s="2">
-        <v>20.06</v>
+        <v>43.68</v>
       </c>
       <c r="F241" s="4">
         <f>B241/E241</f>
       </c>
       <c r="G241" s="2" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>21</v>
@@ -10276,21 +10127,21 @@
     </row>
     <row r="242" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B242" s="3">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="2">
-        <v>23.62</v>
+        <v>20.06</v>
       </c>
       <c r="F242" s="4">
         <f>B242/E242</f>
       </c>
       <c r="G242" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>21</v>
@@ -10307,34 +10158,30 @@
     </row>
     <row r="243" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="B243" s="3">
-        <v>300</v>
-      </c>
-      <c r="C243" s="2">
-        <v>2</v>
-      </c>
-      <c r="D243" s="2">
-        <v>1</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
       <c r="E243" s="2">
-        <v>38</v>
+        <v>23.62</v>
       </c>
       <c r="F243" s="4">
         <f>B243/E243</f>
       </c>
       <c r="G243" s="2" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K243" s="2" t="s">
         <v>336</v>
@@ -10345,7 +10192,7 @@
         <v>227</v>
       </c>
       <c r="B244" s="3">
-        <v>635</v>
+        <v>300</v>
       </c>
       <c r="C244" s="2">
         <v>2</v>
@@ -10354,7 +10201,7 @@
         <v>1</v>
       </c>
       <c r="E244" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F244" s="4">
         <f>B244/E244</f>
@@ -10380,16 +10227,16 @@
         <v>227</v>
       </c>
       <c r="B245" s="3">
-        <v>849</v>
+        <v>635</v>
       </c>
       <c r="C245" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245" s="2">
         <v>1</v>
       </c>
       <c r="E245" s="2">
-        <v>10.8</v>
+        <v>39</v>
       </c>
       <c r="F245" s="4">
         <f>B245/E245</f>
@@ -10401,10 +10248,10 @@
         <v>13</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J245" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K245" s="2" t="s">
         <v>338</v>
@@ -10424,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="E246" s="2">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F246" s="4">
         <f>B246/E246</f>
@@ -10450,7 +10297,7 @@
         <v>227</v>
       </c>
       <c r="B247" s="3">
-        <v>899</v>
+        <v>849</v>
       </c>
       <c r="C247" s="2">
         <v>1</v>
@@ -10459,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="E247" s="2">
-        <v>12.6</v>
+        <v>10.7</v>
       </c>
       <c r="F247" s="4">
         <f>B247/E247</f>
@@ -10485,16 +10332,16 @@
         <v>227</v>
       </c>
       <c r="B248" s="3">
-        <v>685</v>
+        <v>899</v>
       </c>
       <c r="C248" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248" s="2">
         <v>1</v>
       </c>
       <c r="E248" s="2">
-        <v>52</v>
+        <v>12.6</v>
       </c>
       <c r="F248" s="4">
         <f>B248/E248</f>
@@ -10506,10 +10353,10 @@
         <v>13</v>
       </c>
       <c r="I248" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J248" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K248" s="2" t="s">
         <v>341</v>
@@ -10526,7 +10373,7 @@
         <v>1</v>
       </c>
       <c r="D249" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" s="2">
         <v>13</v>
@@ -10555,16 +10402,16 @@
         <v>227</v>
       </c>
       <c r="B250" s="3">
-        <v>405</v>
+        <v>685</v>
       </c>
       <c r="C250" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D250" s="2">
         <v>1</v>
       </c>
       <c r="E250" s="2">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F250" s="4">
         <f>B250/E250</f>
@@ -10576,7 +10423,7 @@
         <v>13</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>16</v>
@@ -10590,16 +10437,16 @@
         <v>227</v>
       </c>
       <c r="B251" s="3">
-        <v>520</v>
+        <v>899</v>
       </c>
       <c r="C251" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251" s="2">
         <v>1</v>
       </c>
       <c r="E251" s="2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F251" s="4">
         <f>B251/E251</f>
@@ -10614,7 +10461,7 @@
         <v>13</v>
       </c>
       <c r="J251" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K251" s="2" t="s">
         <v>344</v>
@@ -10625,16 +10472,16 @@
         <v>227</v>
       </c>
       <c r="B252" s="3">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C252" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D252" s="2">
         <v>1</v>
       </c>
       <c r="E252" s="2">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="F252" s="4">
         <f>B252/E252</f>
@@ -10660,7 +10507,7 @@
         <v>227</v>
       </c>
       <c r="B253" s="3">
-        <v>900</v>
+        <v>360</v>
       </c>
       <c r="C253" s="2">
         <v>2</v>
@@ -10669,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="E253" s="2">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F253" s="4">
         <f>B253/E253</f>
@@ -10678,13 +10525,13 @@
         <v>157</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I253" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J253" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K253" s="2" t="s">
         <v>346</v>
@@ -10695,7 +10542,7 @@
         <v>227</v>
       </c>
       <c r="B254" s="3">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
@@ -10704,7 +10551,7 @@
         <v>1</v>
       </c>
       <c r="E254" s="2">
-        <v>37.2</v>
+        <v>42</v>
       </c>
       <c r="F254" s="4">
         <f>B254/E254</f>
@@ -10730,16 +10577,16 @@
         <v>227</v>
       </c>
       <c r="B255" s="3">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="C255" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D255" s="2">
         <v>1</v>
       </c>
       <c r="E255" s="2">
-        <v>95.2</v>
+        <v>53</v>
       </c>
       <c r="F255" s="4">
         <f>B255/E255</f>
@@ -10751,7 +10598,7 @@
         <v>13</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>13</v>
@@ -10768,13 +10615,13 @@
         <v>550</v>
       </c>
       <c r="C256" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D256" s="2">
         <v>1</v>
       </c>
       <c r="E256" s="2">
-        <v>69</v>
+        <v>37.2</v>
       </c>
       <c r="F256" s="4">
         <f>B256/E256</f>
@@ -10783,13 +10630,13 @@
         <v>157</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J256" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K256" s="2" t="s">
         <v>349</v>
@@ -10800,16 +10647,16 @@
         <v>227</v>
       </c>
       <c r="B257" s="3">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C257" s="2">
         <v>4</v>
       </c>
       <c r="D257" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E257" s="2">
-        <v>73</v>
+        <v>95.2</v>
       </c>
       <c r="F257" s="4">
         <f>B257/E257</f>
@@ -10835,16 +10682,16 @@
         <v>227</v>
       </c>
       <c r="B258" s="3">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C258" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D258" s="2">
         <v>1</v>
       </c>
       <c r="E258" s="2">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F258" s="4">
         <f>B258/E258</f>
@@ -10853,13 +10700,13 @@
         <v>157</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I258" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J258" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K258" s="2" t="s">
         <v>351</v>
@@ -10870,16 +10717,16 @@
         <v>227</v>
       </c>
       <c r="B259" s="3">
-        <v>490</v>
+        <v>32</v>
       </c>
       <c r="C259" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D259" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E259" s="2">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F259" s="4">
         <f>B259/E259</f>
@@ -10891,7 +10738,7 @@
         <v>13</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>13</v>
@@ -10905,7 +10752,7 @@
         <v>227</v>
       </c>
       <c r="B260" s="3">
-        <v>500</v>
+        <v>555</v>
       </c>
       <c r="C260" s="2">
         <v>2</v>
@@ -10914,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="E260" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F260" s="4">
         <f>B260/E260</f>
@@ -10926,10 +10773,10 @@
         <v>13</v>
       </c>
       <c r="I260" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K260" s="2" t="s">
         <v>353</v>
@@ -10940,16 +10787,16 @@
         <v>227</v>
       </c>
       <c r="B261" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C261" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D261" s="2">
         <v>1</v>
       </c>
       <c r="E261" s="2">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="F261" s="4">
         <f>B261/E261</f>
@@ -10958,10 +10805,10 @@
         <v>157</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I261" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>13</v>
@@ -10975,7 +10822,7 @@
         <v>227</v>
       </c>
       <c r="B262" s="3">
-        <v>367</v>
+        <v>490</v>
       </c>
       <c r="C262" s="2">
         <v>2</v>
@@ -10984,7 +10831,7 @@
         <v>1</v>
       </c>
       <c r="E262" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F262" s="4">
         <f>B262/E262</f>
@@ -10996,7 +10843,7 @@
         <v>13</v>
       </c>
       <c r="I262" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>13</v>
@@ -11010,16 +10857,16 @@
         <v>227</v>
       </c>
       <c r="B263" s="3">
-        <v>977</v>
+        <v>200</v>
       </c>
       <c r="C263" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D263" s="2">
         <v>1</v>
       </c>
       <c r="E263" s="2">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="F263" s="4">
         <f>B263/E263</f>
@@ -11034,7 +10881,7 @@
         <v>16</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K263" s="2" t="s">
         <v>356</v>
@@ -11045,14 +10892,16 @@
         <v>227</v>
       </c>
       <c r="B264" s="3">
-        <v>490</v>
+        <v>367</v>
       </c>
       <c r="C264" s="2">
         <v>2</v>
       </c>
-      <c r="D264" s="2"/>
+      <c r="D264" s="2">
+        <v>1</v>
+      </c>
       <c r="E264" s="2">
-        <v>39.3</v>
+        <v>51</v>
       </c>
       <c r="F264" s="4">
         <f>B264/E264</f>
@@ -11061,7 +10910,7 @@
         <v>157</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I264" s="2" t="s">
         <v>16</v>
@@ -11078,28 +10927,31 @@
         <v>227</v>
       </c>
       <c r="B265" s="3">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="C265" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D265" s="2">
         <v>1</v>
       </c>
       <c r="E265" s="2">
-        <v>105</v>
+        <v>33</v>
+      </c>
+      <c r="F265" s="4">
+        <f>B265/E265</f>
       </c>
       <c r="G265" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I265" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K265" s="2" t="s">
         <v>358</v>
@@ -11110,16 +10962,16 @@
         <v>227</v>
       </c>
       <c r="B266" s="3">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="C266" s="2">
         <v>4</v>
       </c>
       <c r="D266" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F266" s="4">
         <f>B266/E266</f>
@@ -11128,13 +10980,13 @@
         <v>157</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I266" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J266" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K266" s="2" t="s">
         <v>359</v>
@@ -11145,16 +10997,14 @@
         <v>227</v>
       </c>
       <c r="B267" s="3">
-        <v>914</v>
+        <v>490</v>
       </c>
       <c r="C267" s="2">
-        <v>4</v>
-      </c>
-      <c r="D267" s="2">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D267" s="2"/>
       <c r="E267" s="2">
-        <v>70</v>
+        <v>39.3</v>
       </c>
       <c r="F267" s="4">
         <f>B267/E267</f>
@@ -11163,10 +11013,10 @@
         <v>157</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I267" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>13</v>
@@ -11180,19 +11030,16 @@
         <v>227</v>
       </c>
       <c r="B268" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C268" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D268" s="2">
         <v>1</v>
       </c>
       <c r="E268" s="2">
-        <v>35</v>
-      </c>
-      <c r="F268" s="4">
-        <f>B268/E268</f>
+        <v>105</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>157</v>
@@ -11215,16 +11062,16 @@
         <v>227</v>
       </c>
       <c r="B269" s="3">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="C269" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D269" s="2">
         <v>1</v>
       </c>
       <c r="E269" s="2">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="F269" s="4">
         <f>B269/E269</f>
@@ -11233,13 +11080,13 @@
         <v>157</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J269" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K269" s="2" t="s">
         <v>362</v>
@@ -11250,16 +11097,16 @@
         <v>227</v>
       </c>
       <c r="B270" s="3">
-        <v>525</v>
+        <v>914</v>
       </c>
       <c r="C270" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D270" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E270" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F270" s="4">
         <f>B270/E270</f>
@@ -11285,16 +11132,16 @@
         <v>227</v>
       </c>
       <c r="B271" s="3">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="C271" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D271" s="2">
         <v>1</v>
       </c>
       <c r="E271" s="2">
-        <v>41.8</v>
+        <v>35</v>
       </c>
       <c r="F271" s="4">
         <f>B271/E271</f>
@@ -11306,7 +11153,7 @@
         <v>13</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>13</v>
@@ -11320,31 +11167,31 @@
         <v>227</v>
       </c>
       <c r="B272" s="3">
-        <v>685</v>
+        <v>100</v>
       </c>
       <c r="C272" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D272" s="2">
         <v>1</v>
       </c>
       <c r="E272" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F272" s="4">
         <f>B272/E272</f>
       </c>
       <c r="G272" s="2" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J272" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K272" s="2" t="s">
         <v>365</v>
@@ -11355,31 +11202,31 @@
         <v>227</v>
       </c>
       <c r="B273" s="3">
-        <v>130</v>
+        <v>525</v>
       </c>
       <c r="C273" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D273" s="2">
         <v>1</v>
       </c>
       <c r="E273" s="2">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F273" s="4">
         <f>B273/E273</f>
       </c>
       <c r="G273" s="2" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I273" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J273" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K273" s="2" t="s">
         <v>366</v>
@@ -11390,28 +11237,28 @@
         <v>227</v>
       </c>
       <c r="B274" s="3">
-        <v>915</v>
+        <v>280</v>
       </c>
       <c r="C274" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D274" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E274" s="2">
-        <v>220</v>
+        <v>41.8</v>
       </c>
       <c r="F274" s="4">
         <f>B274/E274</f>
       </c>
       <c r="G274" s="2" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>13</v>
@@ -11425,28 +11272,28 @@
         <v>227</v>
       </c>
       <c r="B275" s="3">
-        <v>890</v>
+        <v>500</v>
       </c>
       <c r="C275" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D275" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E275" s="2">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="F275" s="4">
         <f>B275/E275</f>
       </c>
       <c r="G275" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I275" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>13</v>
@@ -11460,7 +11307,7 @@
         <v>227</v>
       </c>
       <c r="B276" s="3">
-        <v>699</v>
+        <v>912</v>
       </c>
       <c r="C276" s="2">
         <v>3</v>
@@ -11469,13 +11316,13 @@
         <v>1</v>
       </c>
       <c r="E276" s="2">
-        <v>78.1</v>
+        <v>75</v>
       </c>
       <c r="F276" s="4">
         <f>B276/E276</f>
       </c>
       <c r="G276" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>13</v>
@@ -11495,28 +11342,28 @@
         <v>227</v>
       </c>
       <c r="B277" s="3">
-        <v>945</v>
+        <v>400</v>
       </c>
       <c r="C277" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D277" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" s="2">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="F277" s="4">
         <f>B277/E277</f>
       </c>
       <c r="G277" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>13</v>
@@ -11530,31 +11377,31 @@
         <v>227</v>
       </c>
       <c r="B278" s="3">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="C278" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D278" s="2">
         <v>1</v>
       </c>
       <c r="E278" s="2">
-        <v>33</v>
+        <v>87.2</v>
       </c>
       <c r="F278" s="4">
         <f>B278/E278</f>
       </c>
       <c r="G278" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K278" s="2" t="s">
         <v>371</v>
@@ -11565,31 +11412,31 @@
         <v>227</v>
       </c>
       <c r="B279" s="3">
-        <v>830</v>
+        <v>912</v>
       </c>
       <c r="C279" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D279" s="2">
         <v>1</v>
       </c>
       <c r="E279" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="F279" s="4">
         <f>B279/E279</f>
       </c>
       <c r="G279" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I279" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J279" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K279" s="2" t="s">
         <v>372</v>
@@ -11600,7 +11447,7 @@
         <v>227</v>
       </c>
       <c r="B280" s="3">
-        <v>53</v>
+        <v>400</v>
       </c>
       <c r="C280" s="2">
         <v>2</v>
@@ -11609,22 +11456,22 @@
         <v>1</v>
       </c>
       <c r="E280" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F280" s="4">
         <f>B280/E280</f>
       </c>
       <c r="G280" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I280" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K280" s="2" t="s">
         <v>373</v>
@@ -11635,28 +11482,28 @@
         <v>227</v>
       </c>
       <c r="B281" s="3">
-        <v>900</v>
+        <v>275</v>
       </c>
       <c r="C281" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281" s="2">
         <v>1</v>
       </c>
       <c r="E281" s="2">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F281" s="4">
         <f>B281/E281</f>
       </c>
       <c r="G281" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>13</v>
@@ -11670,28 +11517,28 @@
         <v>227</v>
       </c>
       <c r="B282" s="3">
-        <v>915</v>
+        <v>990</v>
       </c>
       <c r="C282" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E282" s="2">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="F282" s="4">
         <f>B282/E282</f>
       </c>
       <c r="G282" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>13</v>
@@ -11705,28 +11552,28 @@
         <v>227</v>
       </c>
       <c r="B283" s="3">
-        <v>945</v>
+        <v>490</v>
       </c>
       <c r="C283" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D283" s="2">
         <v>1</v>
       </c>
       <c r="E283" s="2">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F283" s="4">
         <f>B283/E283</f>
       </c>
       <c r="G283" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I283" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>13</v>
@@ -11740,28 +11587,28 @@
         <v>227</v>
       </c>
       <c r="B284" s="3">
-        <v>775</v>
+        <v>426</v>
       </c>
       <c r="C284" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D284" s="2">
         <v>1</v>
       </c>
       <c r="E284" s="2">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F284" s="4">
         <f>B284/E284</f>
       </c>
       <c r="G284" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I284" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>13</v>
@@ -11775,28 +11622,28 @@
         <v>227</v>
       </c>
       <c r="B285" s="3">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="C285" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D285" s="2">
         <v>1</v>
       </c>
       <c r="E285" s="2">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F285" s="4">
         <f>B285/E285</f>
       </c>
       <c r="G285" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I285" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>13</v>
@@ -11810,22 +11657,22 @@
         <v>227</v>
       </c>
       <c r="B286" s="3">
-        <v>890</v>
+        <v>570</v>
       </c>
       <c r="C286" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D286" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E286" s="2">
-        <v>220</v>
+        <v>64</v>
       </c>
       <c r="F286" s="4">
         <f>B286/E286</f>
       </c>
       <c r="G286" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>13</v>
@@ -11834,7 +11681,7 @@
         <v>16</v>
       </c>
       <c r="J286" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K286" s="2" t="s">
         <v>379</v>
@@ -11845,28 +11692,28 @@
         <v>227</v>
       </c>
       <c r="B287" s="3">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="C287" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D287" s="2">
         <v>1</v>
       </c>
       <c r="E287" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F287" s="4">
         <f>B287/E287</f>
       </c>
       <c r="G287" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>13</v>
@@ -11880,31 +11727,31 @@
         <v>227</v>
       </c>
       <c r="B288" s="3">
-        <v>950</v>
+        <v>700</v>
       </c>
       <c r="C288" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D288" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E288" s="2">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F288" s="4">
         <f>B288/E288</f>
       </c>
       <c r="G288" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J288" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K288" s="2" t="s">
         <v>381</v>
@@ -11915,25 +11762,25 @@
         <v>227</v>
       </c>
       <c r="B289" s="3">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="C289" s="2">
         <v>4</v>
       </c>
       <c r="D289" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F289" s="4">
         <f>B289/E289</f>
       </c>
       <c r="G289" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I289" s="2" t="s">
         <v>13</v>
@@ -11950,28 +11797,28 @@
         <v>227</v>
       </c>
       <c r="B290" s="3">
-        <v>955</v>
+        <v>490</v>
       </c>
       <c r="C290" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D290" s="2">
         <v>1</v>
       </c>
       <c r="E290" s="2">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="F290" s="4">
         <f>B290/E290</f>
       </c>
       <c r="G290" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>13</v>
@@ -11985,22 +11832,22 @@
         <v>227</v>
       </c>
       <c r="B291" s="3">
-        <v>310</v>
+        <v>800</v>
       </c>
       <c r="C291" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D291" s="2">
         <v>1</v>
       </c>
       <c r="E291" s="2">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F291" s="4">
         <f>B291/E291</f>
       </c>
       <c r="G291" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>13</v>
@@ -12020,7 +11867,7 @@
         <v>227</v>
       </c>
       <c r="B292" s="3">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="C292" s="2">
         <v>4</v>
@@ -12029,22 +11876,19 @@
         <v>1</v>
       </c>
       <c r="E292" s="2">
-        <v>70</v>
-      </c>
-      <c r="F292" s="4">
-        <f>B292/E292</f>
+        <v>87</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I292" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J292" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K292" s="2" t="s">
         <v>385</v>
@@ -12055,22 +11899,22 @@
         <v>227</v>
       </c>
       <c r="B293" s="3">
-        <v>995</v>
+        <v>570</v>
       </c>
       <c r="C293" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D293" s="2">
         <v>1</v>
       </c>
       <c r="E293" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F293" s="4">
         <f>B293/E293</f>
       </c>
       <c r="G293" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>13</v>
@@ -12079,7 +11923,7 @@
         <v>16</v>
       </c>
       <c r="J293" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K293" s="2" t="s">
         <v>386</v>
@@ -12090,22 +11934,22 @@
         <v>227</v>
       </c>
       <c r="B294" s="3">
-        <v>895</v>
+        <v>261</v>
       </c>
       <c r="C294" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D294" s="2">
         <v>1</v>
       </c>
       <c r="E294" s="2">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="F294" s="4">
         <f>B294/E294</f>
       </c>
       <c r="G294" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>13</v>
@@ -12125,22 +11969,22 @@
         <v>227</v>
       </c>
       <c r="B295" s="3">
-        <v>845</v>
+        <v>38</v>
       </c>
       <c r="C295" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D295" s="2">
         <v>1</v>
       </c>
       <c r="E295" s="2">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="F295" s="4">
         <f>B295/E295</f>
       </c>
       <c r="G295" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>13</v>
@@ -12149,7 +11993,7 @@
         <v>16</v>
       </c>
       <c r="J295" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K295" s="2" t="s">
         <v>388</v>
@@ -12160,28 +12004,26 @@
         <v>227</v>
       </c>
       <c r="B296" s="3">
-        <v>990</v>
+        <v>620</v>
       </c>
       <c r="C296" s="2">
-        <v>5</v>
-      </c>
-      <c r="D296" s="2">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D296" s="2"/>
       <c r="E296" s="2">
-        <v>120</v>
+        <v>9.9</v>
       </c>
       <c r="F296" s="4">
         <f>B296/E296</f>
       </c>
       <c r="G296" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I296" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>13</v>
@@ -12195,28 +12037,28 @@
         <v>227</v>
       </c>
       <c r="B297" s="3">
-        <v>170</v>
+        <v>590</v>
       </c>
       <c r="C297" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D297" s="2">
         <v>1</v>
       </c>
       <c r="E297" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F297" s="4">
         <f>B297/E297</f>
       </c>
       <c r="G297" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>13</v>
@@ -12230,22 +12072,22 @@
         <v>227</v>
       </c>
       <c r="B298" s="3">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="C298" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D298" s="2">
         <v>1</v>
       </c>
       <c r="E298" s="2">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="F298" s="4">
         <f>B298/E298</f>
       </c>
       <c r="G298" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>13</v>
@@ -12254,7 +12096,7 @@
         <v>13</v>
       </c>
       <c r="J298" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K298" s="2" t="s">
         <v>391</v>
@@ -12265,25 +12107,25 @@
         <v>227</v>
       </c>
       <c r="B299" s="3">
-        <v>885</v>
+        <v>935</v>
       </c>
       <c r="C299" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D299" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E299" s="2">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="F299" s="4">
         <f>B299/E299</f>
       </c>
       <c r="G299" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I299" s="2" t="s">
         <v>16</v>
@@ -12300,7 +12142,7 @@
         <v>227</v>
       </c>
       <c r="B300" s="3">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="C300" s="2">
         <v>4</v>
@@ -12309,16 +12151,16 @@
         <v>1</v>
       </c>
       <c r="E300" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F300" s="4">
         <f>B300/E300</f>
       </c>
       <c r="G300" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I300" s="2" t="s">
         <v>13</v>
@@ -12335,31 +12177,31 @@
         <v>227</v>
       </c>
       <c r="B301" s="3">
-        <v>985</v>
+        <v>600</v>
       </c>
       <c r="C301" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D301" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E301" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F301" s="4">
         <f>B301/E301</f>
       </c>
       <c r="G301" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I301" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J301" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K301" s="2" t="s">
         <v>394</v>
@@ -12370,31 +12212,31 @@
         <v>227</v>
       </c>
       <c r="B302" s="3">
-        <v>955</v>
+        <v>253</v>
       </c>
       <c r="C302" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D302" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E302" s="2">
-        <v>110</v>
+        <v>50.4</v>
       </c>
       <c r="F302" s="4">
         <f>B302/E302</f>
       </c>
       <c r="G302" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I302" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J302" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K302" s="2" t="s">
         <v>395</v>
@@ -12405,31 +12247,31 @@
         <v>227</v>
       </c>
       <c r="B303" s="3">
-        <v>985</v>
+        <v>700</v>
       </c>
       <c r="C303" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D303" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E303" s="2">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="F303" s="4">
         <f>B303/E303</f>
       </c>
       <c r="G303" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I303" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J303" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K303" s="2" t="s">
         <v>396</v>
@@ -12440,16 +12282,14 @@
         <v>227</v>
       </c>
       <c r="B304" s="3">
-        <v>500</v>
+        <v>795</v>
       </c>
       <c r="C304" s="2">
-        <v>2</v>
-      </c>
-      <c r="D304" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D304" s="2"/>
       <c r="E304" s="2">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F304" s="4">
         <f>B304/E304</f>
@@ -12461,7 +12301,7 @@
         <v>13</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>13</v>
@@ -12475,16 +12315,16 @@
         <v>227</v>
       </c>
       <c r="B305" s="3">
-        <v>912</v>
+        <v>25</v>
       </c>
       <c r="C305" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D305" s="2">
         <v>1</v>
       </c>
       <c r="E305" s="2">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F305" s="4">
         <f>B305/E305</f>
@@ -12496,7 +12336,7 @@
         <v>13</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>16</v>
@@ -12510,7 +12350,7 @@
         <v>227</v>
       </c>
       <c r="B306" s="3">
-        <v>400</v>
+        <v>526</v>
       </c>
       <c r="C306" s="2">
         <v>2</v>
@@ -12519,13 +12359,13 @@
         <v>1</v>
       </c>
       <c r="E306" s="2">
-        <v>47</v>
+        <v>50.1</v>
       </c>
       <c r="F306" s="4">
         <f>B306/E306</f>
       </c>
       <c r="G306" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>16</v>
@@ -12534,10 +12374,10 @@
         <v>13</v>
       </c>
       <c r="J306" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K306" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="307" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12545,34 +12385,32 @@
         <v>227</v>
       </c>
       <c r="B307" s="3">
-        <v>890</v>
+        <v>404</v>
       </c>
       <c r="C307" s="2">
-        <v>4</v>
-      </c>
-      <c r="D307" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D307" s="2"/>
       <c r="E307" s="2">
-        <v>87.2</v>
+        <v>53.6</v>
       </c>
       <c r="F307" s="4">
         <f>B307/E307</f>
       </c>
       <c r="G307" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I307" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J307" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K307" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="308" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12580,7 +12418,7 @@
         <v>227</v>
       </c>
       <c r="B308" s="3">
-        <v>912</v>
+        <v>200</v>
       </c>
       <c r="C308" s="2">
         <v>3</v>
@@ -12589,13 +12427,13 @@
         <v>1</v>
       </c>
       <c r="E308" s="2">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F308" s="4">
         <f>B308/E308</f>
       </c>
       <c r="G308" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>13</v>
@@ -12607,7 +12445,7 @@
         <v>16</v>
       </c>
       <c r="K308" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="309" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12615,34 +12453,31 @@
         <v>227</v>
       </c>
       <c r="B309" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C309" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D309" s="2">
         <v>1</v>
       </c>
       <c r="E309" s="2">
-        <v>47</v>
-      </c>
-      <c r="F309" s="4">
-        <f>B309/E309</f>
+        <v>57</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I309" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J309" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K309" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="310" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12650,22 +12485,22 @@
         <v>227</v>
       </c>
       <c r="B310" s="3">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="C310" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D310" s="2">
         <v>1</v>
       </c>
       <c r="E310" s="2">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F310" s="4">
         <f>B310/E310</f>
       </c>
       <c r="G310" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>13</v>
@@ -12674,10 +12509,10 @@
         <v>13</v>
       </c>
       <c r="J310" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K310" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="311" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12685,7 +12520,7 @@
         <v>227</v>
       </c>
       <c r="B311" s="3">
-        <v>990</v>
+        <v>375</v>
       </c>
       <c r="C311" s="2">
         <v>4</v>
@@ -12694,13 +12529,13 @@
         <v>1</v>
       </c>
       <c r="E311" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F311" s="4">
         <f>B311/E311</f>
       </c>
       <c r="G311" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>13</v>
@@ -12709,10 +12544,10 @@
         <v>13</v>
       </c>
       <c r="J311" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K311" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="312" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12720,22 +12555,22 @@
         <v>227</v>
       </c>
       <c r="B312" s="3">
-        <v>490</v>
+        <v>883</v>
       </c>
       <c r="C312" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D312" s="2">
         <v>1</v>
       </c>
       <c r="E312" s="2">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F312" s="4">
         <f>B312/E312</f>
       </c>
       <c r="G312" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>13</v>
@@ -12747,7 +12582,7 @@
         <v>13</v>
       </c>
       <c r="K312" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="313" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12755,22 +12590,22 @@
         <v>227</v>
       </c>
       <c r="B313" s="3">
-        <v>426</v>
+        <v>636</v>
       </c>
       <c r="C313" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D313" s="2">
         <v>1</v>
       </c>
       <c r="E313" s="2">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="F313" s="4">
         <f>B313/E313</f>
       </c>
       <c r="G313" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>13</v>
@@ -12779,10 +12614,10 @@
         <v>13</v>
       </c>
       <c r="J313" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K313" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="314" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12790,7 +12625,7 @@
         <v>227</v>
       </c>
       <c r="B314" s="3">
-        <v>400</v>
+        <v>259</v>
       </c>
       <c r="C314" s="2">
         <v>2</v>
@@ -12799,25 +12634,25 @@
         <v>1</v>
       </c>
       <c r="E314" s="2">
-        <v>45</v>
+        <v>43.6</v>
       </c>
       <c r="F314" s="4">
         <f>B314/E314</f>
       </c>
       <c r="G314" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K314" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="315" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12825,7 +12660,7 @@
         <v>227</v>
       </c>
       <c r="B315" s="3">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="C315" s="2">
         <v>3</v>
@@ -12834,25 +12669,25 @@
         <v>1</v>
       </c>
       <c r="E315" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F315" s="4">
         <f>B315/E315</f>
       </c>
       <c r="G315" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I315" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K315" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="316" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12860,7 +12695,7 @@
         <v>227</v>
       </c>
       <c r="B316" s="3">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="C316" s="2">
         <v>3</v>
@@ -12869,25 +12704,25 @@
         <v>1</v>
       </c>
       <c r="E316" s="2">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F316" s="4">
         <f>B316/E316</f>
       </c>
       <c r="G316" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I316" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J316" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K316" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="317" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12895,7 +12730,7 @@
         <v>227</v>
       </c>
       <c r="B317" s="3">
-        <v>700</v>
+        <v>227</v>
       </c>
       <c r="C317" s="2">
         <v>3</v>
@@ -12904,25 +12739,25 @@
         <v>1</v>
       </c>
       <c r="E317" s="2">
-        <v>71</v>
+        <v>60.8</v>
       </c>
       <c r="F317" s="4">
         <f>B317/E317</f>
       </c>
       <c r="G317" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I317" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K317" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="318" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12930,34 +12765,34 @@
         <v>227</v>
       </c>
       <c r="B318" s="3">
-        <v>200</v>
+        <v>520</v>
       </c>
       <c r="C318" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D318" s="2">
         <v>1</v>
       </c>
       <c r="E318" s="2">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="F318" s="4">
         <f>B318/E318</f>
       </c>
       <c r="G318" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I318" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K318" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="319" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12965,7 +12800,7 @@
         <v>227</v>
       </c>
       <c r="B319" s="3">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C319" s="2">
         <v>3</v>
@@ -12974,25 +12809,25 @@
         <v>1</v>
       </c>
       <c r="E319" s="2">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F319" s="4">
         <f>B319/E319</f>
       </c>
       <c r="G319" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I319" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J319" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K319" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="320" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13000,34 +12835,34 @@
         <v>227</v>
       </c>
       <c r="B320" s="3">
-        <v>800</v>
+        <v>141</v>
       </c>
       <c r="C320" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D320" s="2">
         <v>1</v>
       </c>
       <c r="E320" s="2">
-        <v>62</v>
+        <v>48.4</v>
       </c>
       <c r="F320" s="4">
         <f>B320/E320</f>
       </c>
       <c r="G320" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J320" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K320" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="321" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13035,7 +12870,7 @@
         <v>227</v>
       </c>
       <c r="B321" s="3">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="C321" s="2">
         <v>4</v>
@@ -13044,10 +12879,13 @@
         <v>1</v>
       </c>
       <c r="E321" s="2">
-        <v>87</v>
+        <v>79.5</v>
+      </c>
+      <c r="F321" s="4">
+        <f>B321/E321</f>
       </c>
       <c r="G321" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>13</v>
@@ -13059,7 +12897,7 @@
         <v>16</v>
       </c>
       <c r="K321" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="322" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13067,34 +12905,34 @@
         <v>227</v>
       </c>
       <c r="B322" s="3">
-        <v>570</v>
+        <v>990</v>
       </c>
       <c r="C322" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D322" s="2">
         <v>1</v>
       </c>
       <c r="E322" s="2">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="F322" s="4">
         <f>B322/E322</f>
       </c>
       <c r="G322" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I322" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J322" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K322" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="323" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13102,7 +12940,7 @@
         <v>227</v>
       </c>
       <c r="B323" s="3">
-        <v>261</v>
+        <v>579</v>
       </c>
       <c r="C323" s="2">
         <v>3</v>
@@ -13111,25 +12949,25 @@
         <v>1</v>
       </c>
       <c r="E323" s="2">
-        <v>43</v>
+        <v>65.7</v>
       </c>
       <c r="F323" s="4">
         <f>B323/E323</f>
       </c>
       <c r="G323" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J323" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K323" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="324" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13137,34 +12975,34 @@
         <v>227</v>
       </c>
       <c r="B324" s="3">
-        <v>38</v>
+        <v>483</v>
       </c>
       <c r="C324" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D324" s="2">
         <v>1</v>
       </c>
       <c r="E324" s="2">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F324" s="4">
         <f>B324/E324</f>
       </c>
       <c r="G324" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J324" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K324" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="325" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13172,32 +13010,34 @@
         <v>227</v>
       </c>
       <c r="B325" s="3">
-        <v>620</v>
+        <v>194</v>
       </c>
       <c r="C325" s="2">
-        <v>1</v>
-      </c>
-      <c r="D325" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D325" s="2">
+        <v>1</v>
+      </c>
       <c r="E325" s="2">
-        <v>9.9</v>
+        <v>33.5</v>
       </c>
       <c r="F325" s="4">
         <f>B325/E325</f>
       </c>
       <c r="G325" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J325" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K325" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="326" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13205,34 +13045,34 @@
         <v>227</v>
       </c>
       <c r="B326" s="3">
-        <v>590</v>
+        <v>346</v>
       </c>
       <c r="C326" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D326" s="2">
         <v>1</v>
       </c>
       <c r="E326" s="2">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F326" s="4">
         <f>B326/E326</f>
       </c>
       <c r="G326" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I326" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J326" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K326" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="327" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13240,34 +13080,32 @@
         <v>227</v>
       </c>
       <c r="B327" s="3">
-        <v>967</v>
+        <v>490</v>
       </c>
       <c r="C327" s="2">
-        <v>5</v>
-      </c>
-      <c r="D327" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D327" s="2"/>
       <c r="E327" s="2">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F327" s="4">
         <f>B327/E327</f>
       </c>
       <c r="G327" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J327" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K327" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="328" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13275,34 +13113,34 @@
         <v>227</v>
       </c>
       <c r="B328" s="3">
-        <v>935</v>
+        <v>387</v>
       </c>
       <c r="C328" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D328" s="2">
         <v>1</v>
       </c>
       <c r="E328" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F328" s="4">
         <f>B328/E328</f>
       </c>
       <c r="G328" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K328" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="329" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13310,34 +13148,34 @@
         <v>227</v>
       </c>
       <c r="B329" s="3">
-        <v>900</v>
+        <v>371</v>
       </c>
       <c r="C329" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D329" s="2">
         <v>1</v>
       </c>
       <c r="E329" s="2">
-        <v>78</v>
+        <v>47.3</v>
       </c>
       <c r="F329" s="4">
         <f>B329/E329</f>
       </c>
       <c r="G329" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J329" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K329" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="330" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13345,34 +13183,34 @@
         <v>227</v>
       </c>
       <c r="B330" s="3">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="C330" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D330" s="2">
         <v>1</v>
       </c>
       <c r="E330" s="2">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F330" s="4">
         <f>B330/E330</f>
       </c>
       <c r="G330" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J330" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K330" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="331" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13380,34 +13218,34 @@
         <v>227</v>
       </c>
       <c r="B331" s="3">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="C331" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D331" s="2">
         <v>1</v>
       </c>
       <c r="E331" s="2">
-        <v>50.4</v>
+        <v>31</v>
       </c>
       <c r="F331" s="4">
         <f>B331/E331</f>
       </c>
       <c r="G331" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J331" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K331" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="332" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13415,34 +13253,34 @@
         <v>227</v>
       </c>
       <c r="B332" s="3">
-        <v>700</v>
+        <v>194</v>
       </c>
       <c r="C332" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D332" s="2">
         <v>1</v>
       </c>
       <c r="E332" s="2">
-        <v>70</v>
+        <v>33.5</v>
       </c>
       <c r="F332" s="4">
         <f>B332/E332</f>
       </c>
       <c r="G332" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J332" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K332" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="333" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13450,23 +13288,25 @@
         <v>227</v>
       </c>
       <c r="B333" s="3">
-        <v>795</v>
+        <v>378</v>
       </c>
       <c r="C333" s="2">
-        <v>1</v>
-      </c>
-      <c r="D333" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D333" s="2">
+        <v>1</v>
+      </c>
       <c r="E333" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F333" s="4">
         <f>B333/E333</f>
       </c>
       <c r="G333" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I333" s="2" t="s">
         <v>16</v>
@@ -13475,7 +13315,7 @@
         <v>13</v>
       </c>
       <c r="K333" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="334" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13483,34 +13323,34 @@
         <v>227</v>
       </c>
       <c r="B334" s="3">
-        <v>25</v>
+        <v>800</v>
       </c>
       <c r="C334" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D334" s="2">
         <v>1</v>
       </c>
       <c r="E334" s="2">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F334" s="4">
         <f>B334/E334</f>
       </c>
       <c r="G334" s="2" t="s">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J334" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K334" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="335" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13518,25 +13358,25 @@
         <v>227</v>
       </c>
       <c r="B335" s="3">
-        <v>526</v>
+        <v>320</v>
       </c>
       <c r="C335" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D335" s="2">
         <v>1</v>
       </c>
       <c r="E335" s="2">
-        <v>50.1</v>
+        <v>110</v>
       </c>
       <c r="F335" s="4">
         <f>B335/E335</f>
       </c>
       <c r="G335" s="2" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I335" s="2" t="s">
         <v>13</v>
@@ -13546,1762 +13386,6 @@
       </c>
       <c r="K335" s="2" t="s">
         <v>429</v>
-      </c>
-    </row>
-    <row r="336" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B336" s="3">
-        <v>404</v>
-      </c>
-      <c r="C336" s="2">
-        <v>2</v>
-      </c>
-      <c r="D336" s="2"/>
-      <c r="E336" s="2">
-        <v>53.6</v>
-      </c>
-      <c r="F336" s="4">
-        <f>B336/E336</f>
-      </c>
-      <c r="G336" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H336" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I336" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J336" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K336" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A337" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B337" s="3">
-        <v>200</v>
-      </c>
-      <c r="C337" s="2">
-        <v>3</v>
-      </c>
-      <c r="D337" s="2">
-        <v>1</v>
-      </c>
-      <c r="E337" s="2">
-        <v>48</v>
-      </c>
-      <c r="F337" s="4">
-        <f>B337/E337</f>
-      </c>
-      <c r="G337" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H337" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I337" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J337" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K337" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="338" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B338" s="3">
-        <v>0</v>
-      </c>
-      <c r="C338" s="2">
-        <v>3</v>
-      </c>
-      <c r="D338" s="2">
-        <v>1</v>
-      </c>
-      <c r="E338" s="2">
-        <v>57</v>
-      </c>
-      <c r="G338" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H338" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I338" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J338" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K338" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="339" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B339" s="3">
-        <v>350</v>
-      </c>
-      <c r="C339" s="2">
-        <v>3</v>
-      </c>
-      <c r="D339" s="2">
-        <v>1</v>
-      </c>
-      <c r="E339" s="2">
-        <v>77</v>
-      </c>
-      <c r="F339" s="4">
-        <f>B339/E339</f>
-      </c>
-      <c r="G339" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H339" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I339" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J339" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K339" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B340" s="3">
-        <v>375</v>
-      </c>
-      <c r="C340" s="2">
-        <v>4</v>
-      </c>
-      <c r="D340" s="2">
-        <v>1</v>
-      </c>
-      <c r="E340" s="2">
-        <v>87</v>
-      </c>
-      <c r="F340" s="4">
-        <f>B340/E340</f>
-      </c>
-      <c r="G340" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H340" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I340" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J340" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K340" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B341" s="3">
-        <v>883</v>
-      </c>
-      <c r="C341" s="2">
-        <v>1</v>
-      </c>
-      <c r="D341" s="2">
-        <v>1</v>
-      </c>
-      <c r="E341" s="2">
-        <v>21</v>
-      </c>
-      <c r="F341" s="4">
-        <f>B341/E341</f>
-      </c>
-      <c r="G341" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H341" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I341" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J341" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K341" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="342" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B342" s="3">
-        <v>636</v>
-      </c>
-      <c r="C342" s="2">
-        <v>5</v>
-      </c>
-      <c r="D342" s="2">
-        <v>1</v>
-      </c>
-      <c r="E342" s="2">
-        <v>102</v>
-      </c>
-      <c r="F342" s="4">
-        <f>B342/E342</f>
-      </c>
-      <c r="G342" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H342" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I342" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J342" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K342" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B343" s="3">
-        <v>259</v>
-      </c>
-      <c r="C343" s="2">
-        <v>2</v>
-      </c>
-      <c r="D343" s="2">
-        <v>1</v>
-      </c>
-      <c r="E343" s="2">
-        <v>43.6</v>
-      </c>
-      <c r="F343" s="4">
-        <f>B343/E343</f>
-      </c>
-      <c r="G343" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H343" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I343" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J343" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K343" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="344" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B344" s="3">
-        <v>700</v>
-      </c>
-      <c r="C344" s="2">
-        <v>3</v>
-      </c>
-      <c r="D344" s="2">
-        <v>1</v>
-      </c>
-      <c r="E344" s="2">
-        <v>53</v>
-      </c>
-      <c r="F344" s="4">
-        <f>B344/E344</f>
-      </c>
-      <c r="G344" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H344" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I344" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J344" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K344" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="345" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B345" s="3">
-        <v>550</v>
-      </c>
-      <c r="C345" s="2">
-        <v>3</v>
-      </c>
-      <c r="D345" s="2">
-        <v>1</v>
-      </c>
-      <c r="E345" s="2">
-        <v>62</v>
-      </c>
-      <c r="F345" s="4">
-        <f>B345/E345</f>
-      </c>
-      <c r="G345" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H345" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I345" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J345" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K345" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="346" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B346" s="3">
-        <v>227</v>
-      </c>
-      <c r="C346" s="2">
-        <v>3</v>
-      </c>
-      <c r="D346" s="2">
-        <v>1</v>
-      </c>
-      <c r="E346" s="2">
-        <v>60.8</v>
-      </c>
-      <c r="F346" s="4">
-        <f>B346/E346</f>
-      </c>
-      <c r="G346" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H346" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I346" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J346" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K346" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="347" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B347" s="3">
-        <v>520</v>
-      </c>
-      <c r="C347" s="2">
-        <v>1</v>
-      </c>
-      <c r="D347" s="2">
-        <v>1</v>
-      </c>
-      <c r="E347" s="2">
-        <v>9</v>
-      </c>
-      <c r="F347" s="4">
-        <f>B347/E347</f>
-      </c>
-      <c r="G347" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H347" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I347" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J347" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K347" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B348" s="3">
-        <v>515</v>
-      </c>
-      <c r="C348" s="2">
-        <v>3</v>
-      </c>
-      <c r="D348" s="2">
-        <v>1</v>
-      </c>
-      <c r="E348" s="2">
-        <v>63</v>
-      </c>
-      <c r="F348" s="4">
-        <f>B348/E348</f>
-      </c>
-      <c r="G348" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H348" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I348" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J348" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K348" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B349" s="3">
-        <v>141</v>
-      </c>
-      <c r="C349" s="2">
-        <v>2</v>
-      </c>
-      <c r="D349" s="2">
-        <v>1</v>
-      </c>
-      <c r="E349" s="2">
-        <v>48.4</v>
-      </c>
-      <c r="F349" s="4">
-        <f>B349/E349</f>
-      </c>
-      <c r="G349" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H349" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I349" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J349" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K349" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B350" s="3">
-        <v>947</v>
-      </c>
-      <c r="C350" s="2">
-        <v>4</v>
-      </c>
-      <c r="D350" s="2">
-        <v>1</v>
-      </c>
-      <c r="E350" s="2">
-        <v>79.5</v>
-      </c>
-      <c r="F350" s="4">
-        <f>B350/E350</f>
-      </c>
-      <c r="G350" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H350" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I350" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J350" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K350" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="351" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B351" s="3">
-        <v>990</v>
-      </c>
-      <c r="C351" s="2">
-        <v>2</v>
-      </c>
-      <c r="D351" s="2">
-        <v>1</v>
-      </c>
-      <c r="E351" s="2">
-        <v>30</v>
-      </c>
-      <c r="F351" s="4">
-        <f>B351/E351</f>
-      </c>
-      <c r="G351" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H351" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I351" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J351" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K351" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="352" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B352" s="3">
-        <v>579</v>
-      </c>
-      <c r="C352" s="2">
-        <v>3</v>
-      </c>
-      <c r="D352" s="2">
-        <v>1</v>
-      </c>
-      <c r="E352" s="2">
-        <v>65.7</v>
-      </c>
-      <c r="F352" s="4">
-        <f>B352/E352</f>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H352" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I352" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J352" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K352" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="353" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B353" s="3">
-        <v>483</v>
-      </c>
-      <c r="C353" s="2">
-        <v>2</v>
-      </c>
-      <c r="D353" s="2">
-        <v>1</v>
-      </c>
-      <c r="E353" s="2">
-        <v>66</v>
-      </c>
-      <c r="F353" s="4">
-        <f>B353/E353</f>
-      </c>
-      <c r="G353" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H353" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I353" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J353" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K353" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="354" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B354" s="3">
-        <v>194</v>
-      </c>
-      <c r="C354" s="2">
-        <v>2</v>
-      </c>
-      <c r="D354" s="2">
-        <v>1</v>
-      </c>
-      <c r="E354" s="2">
-        <v>33.5</v>
-      </c>
-      <c r="F354" s="4">
-        <f>B354/E354</f>
-      </c>
-      <c r="G354" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H354" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I354" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J354" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K354" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="355" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B355" s="3">
-        <v>346</v>
-      </c>
-      <c r="C355" s="2">
-        <v>3</v>
-      </c>
-      <c r="D355" s="2">
-        <v>1</v>
-      </c>
-      <c r="E355" s="2">
-        <v>71</v>
-      </c>
-      <c r="F355" s="4">
-        <f>B355/E355</f>
-      </c>
-      <c r="G355" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H355" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I355" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J355" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K355" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="356" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B356" s="3">
-        <v>490</v>
-      </c>
-      <c r="C356" s="2">
-        <v>1</v>
-      </c>
-      <c r="D356" s="2"/>
-      <c r="E356" s="2">
-        <v>14</v>
-      </c>
-      <c r="F356" s="4">
-        <f>B356/E356</f>
-      </c>
-      <c r="G356" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H356" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I356" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J356" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K356" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="357" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B357" s="3">
-        <v>387</v>
-      </c>
-      <c r="C357" s="2">
-        <v>1</v>
-      </c>
-      <c r="D357" s="2">
-        <v>1</v>
-      </c>
-      <c r="E357" s="2">
-        <v>40</v>
-      </c>
-      <c r="F357" s="4">
-        <f>B357/E357</f>
-      </c>
-      <c r="G357" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H357" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I357" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J357" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K357" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="358" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B358" s="3">
-        <v>371</v>
-      </c>
-      <c r="C358" s="2">
-        <v>2</v>
-      </c>
-      <c r="D358" s="2">
-        <v>1</v>
-      </c>
-      <c r="E358" s="2">
-        <v>47.3</v>
-      </c>
-      <c r="F358" s="4">
-        <f>B358/E358</f>
-      </c>
-      <c r="G358" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H358" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I358" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J358" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K358" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="359" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A359" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B359" s="3">
-        <v>650</v>
-      </c>
-      <c r="C359" s="2">
-        <v>3</v>
-      </c>
-      <c r="D359" s="2">
-        <v>1</v>
-      </c>
-      <c r="E359" s="2">
-        <v>72</v>
-      </c>
-      <c r="F359" s="4">
-        <f>B359/E359</f>
-      </c>
-      <c r="G359" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H359" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I359" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J359" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K359" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="360" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A360" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B360" s="3">
-        <v>220</v>
-      </c>
-      <c r="C360" s="2">
-        <v>2</v>
-      </c>
-      <c r="D360" s="2">
-        <v>1</v>
-      </c>
-      <c r="E360" s="2">
-        <v>31</v>
-      </c>
-      <c r="F360" s="4">
-        <f>B360/E360</f>
-      </c>
-      <c r="G360" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H360" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I360" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J360" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K360" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="361" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B361" s="3">
-        <v>194</v>
-      </c>
-      <c r="C361" s="2">
-        <v>2</v>
-      </c>
-      <c r="D361" s="2">
-        <v>1</v>
-      </c>
-      <c r="E361" s="2">
-        <v>33.5</v>
-      </c>
-      <c r="F361" s="4">
-        <f>B361/E361</f>
-      </c>
-      <c r="G361" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H361" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I361" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J361" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K361" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="362" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B362" s="3">
-        <v>378</v>
-      </c>
-      <c r="C362" s="2">
-        <v>2</v>
-      </c>
-      <c r="D362" s="2">
-        <v>1</v>
-      </c>
-      <c r="E362" s="2">
-        <v>41</v>
-      </c>
-      <c r="F362" s="4">
-        <f>B362/E362</f>
-      </c>
-      <c r="G362" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H362" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I362" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J362" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K362" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="363" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B363" s="3">
-        <v>800</v>
-      </c>
-      <c r="C363" s="2">
-        <v>5</v>
-      </c>
-      <c r="D363" s="2">
-        <v>1</v>
-      </c>
-      <c r="E363" s="2">
-        <v>98</v>
-      </c>
-      <c r="F363" s="4">
-        <f>B363/E363</f>
-      </c>
-      <c r="G363" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H363" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I363" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J363" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K363" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="364" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B364" s="3">
-        <v>320</v>
-      </c>
-      <c r="C364" s="2">
-        <v>5</v>
-      </c>
-      <c r="D364" s="2">
-        <v>1</v>
-      </c>
-      <c r="E364" s="2">
-        <v>110</v>
-      </c>
-      <c r="F364" s="4">
-        <f>B364/E364</f>
-      </c>
-      <c r="G364" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H364" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I364" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J364" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K364" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="365" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B365" s="3">
-        <v>850</v>
-      </c>
-      <c r="C365" s="2">
-        <v>2</v>
-      </c>
-      <c r="D365" s="2">
-        <v>1</v>
-      </c>
-      <c r="E365" s="2">
-        <v>60</v>
-      </c>
-      <c r="F365" s="4">
-        <f>B365/E365</f>
-      </c>
-      <c r="G365" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H365" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I365" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J365" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K365" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="366" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B366" s="3">
-        <v>384</v>
-      </c>
-      <c r="C366" s="2">
-        <v>1</v>
-      </c>
-      <c r="D366" s="2"/>
-      <c r="E366" s="2">
-        <v>18</v>
-      </c>
-      <c r="F366" s="4">
-        <f>B366/E366</f>
-      </c>
-      <c r="G366" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H366" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I366" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J366" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K366" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="367" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B367" s="3">
-        <v>454</v>
-      </c>
-      <c r="C367" s="2">
-        <v>1</v>
-      </c>
-      <c r="D367" s="2"/>
-      <c r="E367" s="2">
-        <v>62</v>
-      </c>
-      <c r="F367" s="4">
-        <f>B367/E367</f>
-      </c>
-      <c r="G367" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H367" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I367" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J367" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K367" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="368" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B368" s="3">
-        <v>891</v>
-      </c>
-      <c r="C368" s="2">
-        <v>1</v>
-      </c>
-      <c r="D368" s="2"/>
-      <c r="E368" s="2">
-        <v>30</v>
-      </c>
-      <c r="F368" s="4">
-        <f>B368/E368</f>
-      </c>
-      <c r="G368" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H368" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I368" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J368" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K368" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="369" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B369" s="3">
-        <v>946</v>
-      </c>
-      <c r="C369" s="2">
-        <v>1</v>
-      </c>
-      <c r="D369" s="2"/>
-      <c r="E369" s="2">
-        <v>38</v>
-      </c>
-      <c r="F369" s="4">
-        <f>B369/E369</f>
-      </c>
-      <c r="G369" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H369" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I369" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J369" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K369" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="370" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B370" s="3">
-        <v>472</v>
-      </c>
-      <c r="C370" s="2">
-        <v>1</v>
-      </c>
-      <c r="D370" s="2"/>
-      <c r="E370" s="2">
-        <v>32</v>
-      </c>
-      <c r="F370" s="4">
-        <f>B370/E370</f>
-      </c>
-      <c r="G370" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H370" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I370" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J370" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K370" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="371" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B371" s="3">
-        <v>100</v>
-      </c>
-      <c r="C371" s="2">
-        <v>3</v>
-      </c>
-      <c r="D371" s="2">
-        <v>1</v>
-      </c>
-      <c r="E371" s="2">
-        <v>72.1</v>
-      </c>
-      <c r="F371" s="4">
-        <f>B371/E371</f>
-      </c>
-      <c r="G371" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H371" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I371" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J371" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K371" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="372" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B372" s="3">
-        <v>32</v>
-      </c>
-      <c r="C372" s="2">
-        <v>3</v>
-      </c>
-      <c r="D372" s="2">
-        <v>2</v>
-      </c>
-      <c r="E372" s="2">
-        <v>58</v>
-      </c>
-      <c r="F372" s="4">
-        <f>B372/E372</f>
-      </c>
-      <c r="G372" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H372" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I372" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J372" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K372" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="373" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B373" s="3">
-        <v>300</v>
-      </c>
-      <c r="C373" s="2">
-        <v>2</v>
-      </c>
-      <c r="D373" s="2">
-        <v>1</v>
-      </c>
-      <c r="E373" s="2">
-        <v>55</v>
-      </c>
-      <c r="F373" s="4">
-        <f>B373/E373</f>
-      </c>
-      <c r="G373" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H373" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I373" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J373" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K373" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="374" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B374" s="3">
-        <v>620</v>
-      </c>
-      <c r="C374" s="2">
-        <v>3</v>
-      </c>
-      <c r="D374" s="2">
-        <v>2</v>
-      </c>
-      <c r="E374" s="2">
-        <v>91</v>
-      </c>
-      <c r="F374" s="4">
-        <f>B374/E374</f>
-      </c>
-      <c r="G374" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H374" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I374" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J374" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K374" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="375" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B375" s="3">
-        <v>545</v>
-      </c>
-      <c r="C375" s="2">
-        <v>1</v>
-      </c>
-      <c r="D375" s="2"/>
-      <c r="E375" s="2">
-        <v>25</v>
-      </c>
-      <c r="F375" s="4">
-        <f>B375/E375</f>
-      </c>
-      <c r="G375" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H375" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I375" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J375" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K375" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="376" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B376" s="3">
-        <v>0</v>
-      </c>
-      <c r="C376" s="2">
-        <v>4</v>
-      </c>
-      <c r="D376" s="2"/>
-      <c r="E376" s="2">
-        <v>80</v>
-      </c>
-      <c r="G376" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H376" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I376" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J376" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K376" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="377" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B377" s="3">
-        <v>200</v>
-      </c>
-      <c r="C377" s="2">
-        <v>8</v>
-      </c>
-      <c r="D377" s="2">
-        <v>5</v>
-      </c>
-      <c r="E377" s="2">
-        <v>175</v>
-      </c>
-      <c r="F377" s="4">
-        <f>B377/E377</f>
-      </c>
-      <c r="G377" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H377" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I377" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J377" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K377" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="378" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B378" s="3">
-        <v>10</v>
-      </c>
-      <c r="C378" s="2">
-        <v>2</v>
-      </c>
-      <c r="D378" s="2">
-        <v>2</v>
-      </c>
-      <c r="E378" s="2">
-        <v>50</v>
-      </c>
-      <c r="F378" s="4">
-        <f>B378/E378</f>
-      </c>
-      <c r="G378" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H378" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I378" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J378" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K378" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="379" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A379" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B379" s="3">
-        <v>915</v>
-      </c>
-      <c r="C379" s="2">
-        <v>2</v>
-      </c>
-      <c r="D379" s="2">
-        <v>1</v>
-      </c>
-      <c r="E379" s="2">
-        <v>38.9</v>
-      </c>
-      <c r="F379" s="4">
-        <f>B379/E379</f>
-      </c>
-      <c r="G379" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H379" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I379" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J379" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K379" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="380" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A380" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B380" s="3">
-        <v>650</v>
-      </c>
-      <c r="C380" s="2">
-        <v>2</v>
-      </c>
-      <c r="D380" s="2">
-        <v>1</v>
-      </c>
-      <c r="E380" s="2">
-        <v>43</v>
-      </c>
-      <c r="F380" s="4">
-        <f>B380/E380</f>
-      </c>
-      <c r="G380" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H380" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I380" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J380" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K380" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="381" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B381" s="3">
-        <v>440</v>
-      </c>
-      <c r="C381" s="2">
-        <v>5</v>
-      </c>
-      <c r="D381" s="2">
-        <v>2</v>
-      </c>
-      <c r="E381" s="2">
-        <v>110</v>
-      </c>
-      <c r="F381" s="4">
-        <f>B381/E381</f>
-      </c>
-      <c r="G381" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H381" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I381" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J381" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K381" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="382" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B382" s="3">
-        <v>100</v>
-      </c>
-      <c r="C382" s="2">
-        <v>1</v>
-      </c>
-      <c r="D382" s="2">
-        <v>1</v>
-      </c>
-      <c r="E382" s="2">
-        <v>36.4</v>
-      </c>
-      <c r="F382" s="4">
-        <f>B382/E382</f>
-      </c>
-      <c r="G382" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H382" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I382" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J382" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K382" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="383" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B383" s="3">
-        <v>363</v>
-      </c>
-      <c r="C383" s="2">
-        <v>2</v>
-      </c>
-      <c r="D383" s="2">
-        <v>1</v>
-      </c>
-      <c r="E383" s="2">
-        <v>30</v>
-      </c>
-      <c r="F383" s="4">
-        <f>B383/E383</f>
-      </c>
-      <c r="G383" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H383" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I383" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J383" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K383" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="384" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A384" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B384" s="3">
-        <v>950</v>
-      </c>
-      <c r="C384" s="2">
-        <v>3</v>
-      </c>
-      <c r="D384" s="2">
-        <v>1</v>
-      </c>
-      <c r="E384" s="2">
-        <v>89</v>
-      </c>
-      <c r="F384" s="4">
-        <f>B384/E384</f>
-      </c>
-      <c r="G384" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H384" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I384" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J384" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K384" s="2" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="385" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B385" s="3">
-        <v>17</v>
-      </c>
-      <c r="C385" s="2">
-        <v>1</v>
-      </c>
-      <c r="D385" s="2">
-        <v>1</v>
-      </c>
-      <c r="E385" s="2"/>
-      <c r="G385" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H385" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I385" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J385" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K385" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="386" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B386" s="3">
-        <v>726</v>
-      </c>
-      <c r="C386" s="2">
-        <v>5</v>
-      </c>
-      <c r="D386" s="2">
-        <v>1</v>
-      </c>
-      <c r="E386" s="2">
-        <v>143</v>
-      </c>
-      <c r="F386" s="4">
-        <f>B386/E386</f>
-      </c>
-      <c r="G386" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H386" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I386" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J386" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K386" s="2" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -15321,212 +13405,212 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>485</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>487</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>490</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>492</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>496</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>499</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>504</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>506</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>507</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>512</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>513</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>514</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>518</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>519</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>520</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>521</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>522</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
